--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,395 +656,407 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21441000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21871000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20553000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20068000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20773000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20612000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19515000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19381000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20953000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20338000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18946000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18109000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19745000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19318000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17698000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17214000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18240000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17798000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17094000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16462000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17438000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16690000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16503000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10144000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10501000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10613000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10404000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10897000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10846000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10802000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10326000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10664000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10365000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9791000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8922000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9253000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9142000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8659000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8518000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8806000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8653000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8410000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8342000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8776000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8420000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17634000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11297000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11370000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9940000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9664000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9876000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9766000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8713000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9055000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10289000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9973000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9155000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9187000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10492000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10176000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9039000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8696000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9434000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9145000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8684000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8120000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8662000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8270000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>125000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>273000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1089,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1169,8 +1182,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,43 +1277,46 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+        <v>1341000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1305,56 +1324,59 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>362000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>222000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>105000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>93000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8985000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>116000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>177000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-218000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>554000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>205000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>154000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>157000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>249000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>157000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>175000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1445,8 +1467,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1476,192 +1501,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17008000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16104000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16391000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15820000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15988000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15673000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15917000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15357000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15785000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15315000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15406000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14324000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14365000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14037000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14221000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13764000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13763000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13509000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22287000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13235000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13551000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>12782000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13916000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4433000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5767000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4162000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4248000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4785000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4939000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3598000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4024000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5168000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5023000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3540000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3785000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5380000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5281000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3477000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3450000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4477000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4289000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3227000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3887000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3908000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2587000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1694,468 +1726,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>311000</v>
+      </c>
+      <c r="E20" s="3">
         <v>260000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>311000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>262000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>221000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>181000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>167000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>156000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>177000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>121000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>141000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>198000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-360000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>152000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>141000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>148000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>155000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>162000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>239000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>182000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>167000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>161000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>90000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>358000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>218000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>94000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>72000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5465000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6729000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5179000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5202000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5659000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5783000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4487000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4870000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6029000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5855000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4391000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4666000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5691000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6104000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4432000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4397000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5309000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5174000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4120000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4704000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4712000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3311000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E22" s="3">
         <v>225000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>240000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>222000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>171000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>123000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>115000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>109000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>106000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>117000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>106000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>143000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>136000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>157000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>100000</v>
       </c>
       <c r="S22" s="3">
         <v>100000</v>
       </c>
       <c r="T22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="U22" s="3">
         <v>108000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>111000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>131000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>138000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>129000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>272000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>133000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>244000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>115000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>116000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>96000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>122000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4496000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5802000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4233000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4288000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4835000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4997000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3650000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4071000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5239000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5035000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3564000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3877000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4877000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5297000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3461000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3498000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4532000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4343000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3278000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3916000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3940000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2289000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1003000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1246000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>841000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>864000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>876000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1034000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>592000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>704000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>997000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>909000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>656000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>628000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>990000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>989000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>675000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>541000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>789000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>726000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>172000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>502000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>729000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>499000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>613000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>872000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>881000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>725000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>780000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>695000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,192 +2294,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3493000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4556000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3392000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3424000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3959000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3963000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3058000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3367000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4242000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4126000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2908000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3249000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3887000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4308000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2786000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2957000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3743000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3617000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2776000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3216000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3211000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1790000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3398000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4450000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3312000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3328000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3863000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3868000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2979000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3287000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4153000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4042000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2832000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3204000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3788000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4211000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2730000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2853000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3653000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3528000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2681000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3129000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3133000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1724000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2522,8 +2579,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,17 +2632,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2590,18 +2650,18 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>100000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
@@ -2609,13 +2669,16 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2706,8 +2769,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2798,192 +2864,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-311000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-260000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-311000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-262000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-221000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-181000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-167000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-156000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-177000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-121000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-141000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-198000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>360000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-141000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-148000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-155000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-162000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-239000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-182000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-167000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-161000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>26000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>497000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3398000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4450000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3312000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3328000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3863000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3868000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2979000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3287000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4153000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4042000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2832000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3204000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3788000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4211000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2730000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2853000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3653000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3528000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2681000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3129000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3133000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1824000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3074,197 +3149,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3398000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4450000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3312000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3328000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3863000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3868000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2979000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3287000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4153000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4042000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2832000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3204000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3788000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4211000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2730000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2853000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3653000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3528000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2681000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3129000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3133000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1824000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3297,8 +3381,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3331,100 +3416,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7890000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9733000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8246000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7596000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6854000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6710000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7214000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8526000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11544000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10370000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10288000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10007000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11941000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13392000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16181000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15393000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6279000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9304000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4239000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2738000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3696000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2545000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2569000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3480,411 +3569,426 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>6048000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>7085000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8421000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8708000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9281000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6334000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="E43" s="3">
-        <v>5471000</v>
       </c>
       <c r="F43" s="3">
         <v>5471000</v>
       </c>
       <c r="G43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="H43" s="3">
         <v>5767000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5720000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5143000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5513000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5241000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5662000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4725000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4861000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4819000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5043000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4178000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4640000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5196000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5143000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4951000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5198000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5055000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5035000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4686000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7151000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7117000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7073000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7483000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7541000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7590000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6924000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7101000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6673000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6307000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5983000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6002000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5957000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5707000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5498000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5330000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5521000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5465000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5017000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5358000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5281000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5182000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4738000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1875000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1858000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1755000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1704000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2501000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2372000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2276000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2087000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1997000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2095000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1738000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1938000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1884000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2130000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1777000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1921000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2013000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2218000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1933000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1978000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1876000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2046000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23111000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24940000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22648000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22305000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21866000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22521000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21653000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23416000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25545000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24336000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23091000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22608000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24655000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>26026000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>27987000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>27140000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18917000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21925000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22473000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22312000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>24431000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>23346000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23320000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3894,23 +3998,23 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>63000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>60000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>66000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>113000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>126000</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -3924,8 +4028,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3975,192 +4079,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22132000</v>
+      </c>
+      <c r="E48" s="3">
         <v>21636000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21909000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21564000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21167000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20593000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21195000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21323000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21357000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21392000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21686000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21103000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21416000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20876000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21542000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21314000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22153000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21788000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21271000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20993000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20822000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20590000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20600000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>63218000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63876000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>64442000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64550000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63545000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>62226000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63379000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>64623000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63853000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63997000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>64566000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64270000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>65245000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>64383000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>63693000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>63451000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63978000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63607000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>64488000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>72589000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>72879000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>69144000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>69077000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4251,8 +4364,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4343,100 +4459,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12248000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12079000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11830000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11369000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11077000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10876000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10868000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10729000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10661000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9944000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9964000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8797000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8796000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8614000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7478000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6655000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6675000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6738000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6863000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5779000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5555000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5360000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5313000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4527,100 +4649,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>120709000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122531000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120829000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119851000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117715000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>116282000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117208000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120217000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121416000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119669000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119307000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>116778000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120112000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119899000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120700000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>118560000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>111723000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>114058000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>115095000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>121673000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>123687000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>118440000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118310000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4653,8 +4781,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4687,560 +4816,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14234000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14435000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14598000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13790000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14153000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14845000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14882000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14175000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14154000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14223000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13720000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12134000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12027000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11935000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12071000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10464000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10781000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10951000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11260000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10207000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10266000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10243000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10344000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10616000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11811000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10229000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>13717000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14300000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11717000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8645000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9902000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13331000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11989000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8889000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8773000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8586000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7707000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11183000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>12701000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9153000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9352000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9697000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8911000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>12113000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>10508000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10423000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11100000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10912000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10929000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10523000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10293000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10056000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9554000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10324000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10542000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10377000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10523000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11109000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11131000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10366000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9722000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9731000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10230000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9950000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9054000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9252000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8868000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8469000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7470000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35950000</v>
+      </c>
+      <c r="E60" s="3">
         <v>37158000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35756000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38030000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38746000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36618000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33081000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34401000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38027000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36589000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33132000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32016000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31744000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30008000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32976000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32896000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>30164000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30253000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30011000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>28370000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31247000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>29220000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28237000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23096000</v>
+      </c>
+      <c r="E61" s="3">
         <v>24069000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24378000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22874000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20582000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21286000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>22848000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23767000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22322000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20558000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23099000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21053000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22514000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23948000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23537000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23310000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>18985000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20161000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20395000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21359000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21514000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20779000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20863000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12834000</v>
+      </c>
+      <c r="E62" s="3">
         <v>13290000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13630000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13526000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13662000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14044000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14425000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16303000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16174000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16114000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16422000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16790000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>17314000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17367000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17309000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16413000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16666000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16660000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17110000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16392000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16483000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>15937000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16327000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5331,8 +5479,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5423,8 +5574,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5515,100 +5669,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72174000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74838000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74052000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74711000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73260000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72207000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>70619000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74739000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>76798000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73558000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72929000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>70182000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>71931000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71717000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>74179000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>73020000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>66185000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>67480000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>67901000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>66601000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69697000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>66204000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66017000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5641,8 +5801,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5733,8 +5894,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5825,100 +5989,106 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>809000</v>
+      </c>
+      <c r="E70" s="3">
         <v>812000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>819000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>822000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>831000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>834000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>843000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>846000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>856000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>859000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>870000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>873000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>885000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>888000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>897000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>900000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>911000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>915000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>928000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>933000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>946000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>951000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>967000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>972000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>986000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>991000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6009,100 +6179,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>121617000</v>
+      </c>
+      <c r="E72" s="3">
         <v>120443000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>118170000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>117082000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>115858000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>114163000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>112429000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>111645000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>110393000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>108361000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>106374000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>105674000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>104361000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>102539000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>100239000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>99474000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>98414000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>96625000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>94918000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>102103000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>101170000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>99831000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>98641000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6193,8 +6369,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6285,8 +6464,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6377,100 +6559,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47726000</v>
+      </c>
+      <c r="E76" s="3">
         <v>46881000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45958000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44318000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43624000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43241000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45746000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44632000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43762000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45252000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45508000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45723000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>47296000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47294000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45624000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44640000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44627000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45663000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46266000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>54139000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53044000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>51285000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>51326000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6561,197 +6749,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3398000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4450000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3312000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3328000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3863000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3868000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2979000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3287000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4153000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4042000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2832000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3204000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3788000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4211000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2730000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2853000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3653000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3528000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2681000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3129000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3133000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1824000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6784,100 +6981,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>721000</v>
+      </c>
+      <c r="E83" s="3">
         <v>702000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>706000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>692000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>653000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>663000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>722000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>690000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>684000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>711000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>710000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>683000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>671000</v>
       </c>
       <c r="P83" s="3">
         <v>671000</v>
       </c>
       <c r="Q83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="R83" s="3">
         <v>814000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>799000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>677000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>723000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>820000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>711000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>650000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>643000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>750000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>716000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>676000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>692000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>720000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>665000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>707000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6968,8 +7169,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7060,8 +7264,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7152,8 +7359,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7244,8 +7454,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7336,100 +7549,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5101000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4903000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5341000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3863000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3574000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4070000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3713000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3246000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5121000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4643000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4121000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4087000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5424000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4739000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4806000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4064000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4364000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4169000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4151000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3517000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4007000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3567000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4199000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7462,100 +7681,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-817000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-925000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-734000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-730000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-708000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-890000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-692000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-747000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-626000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-714000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-656000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-567000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-850000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-658000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-731000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-605000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-814000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-752000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-701000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-907000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7646,8 +7869,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7738,100 +7964,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1002000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-798000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-490000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-832000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-682000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-960000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-791000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-665000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-549000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-829000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-659000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-725000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-650000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5079000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>647000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>573000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>97000</v>
       </c>
       <c r="Z94" s="3">
         <v>97000</v>
       </c>
       <c r="AA94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>100000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7864,100 +8096,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2288000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2290000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2482000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-4899000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>566000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AA96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AB96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8048,8 +8284,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8140,8 +8379,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8232,280 +8474,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6049000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>5945000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1032000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-156000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>53000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-235000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-185000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-56000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-129000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-127000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>36000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-81000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>115000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>40000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-170000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>56000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-65000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>18000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-43000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-70000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-192000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>82000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>47000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>82000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>159000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>128000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1843000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1487000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>650000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>742000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>144000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-504000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1174000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>82000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>281000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>788000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9114000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5065000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1501000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-958000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1151000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,407 +656,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="33" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20195000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21441000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21871000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20553000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20068000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20773000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20612000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19515000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19381000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20953000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20338000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18946000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18109000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19745000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19318000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17698000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17214000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18240000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17798000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17094000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16462000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17438000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16690000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9855000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10144000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10501000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10613000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10404000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10897000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10846000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10802000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10326000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10664000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10365000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9791000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8922000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9253000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9142000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8659000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8518000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8806000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8653000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8410000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8342000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8776000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8420000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10340000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11297000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11370000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>9940000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9664000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9876000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9766000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>8713000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9055000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10289000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9973000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9155000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9187000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10492000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10176000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9039000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8696000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9434000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9145000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8684000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8120000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8662000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8270000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>125000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>273000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1185,8 +1198,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1280,16 +1296,19 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1341000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1306,20 +1325,20 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1327,56 +1346,59 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>362000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>222000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>105000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>93000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8985000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>116000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>177000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-218000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>554000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>205000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>154000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>157000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>249000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>157000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>175000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1470,8 +1492,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1502,198 +1527,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15735000</v>
+      </c>
+      <c r="E17" s="3">
         <v>17008000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16104000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16391000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15820000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15988000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15673000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15917000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15357000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15785000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15315000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15406000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14324000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14365000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14037000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14221000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13764000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13763000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13509000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22287000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13235000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13551000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>12782000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4460000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4433000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5767000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4162000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4248000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4785000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4939000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3598000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4024000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5168000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5023000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3540000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3785000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5380000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5281000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3477000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3450000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4477000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4289000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3227000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3887000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3908000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1727,483 +1759,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E20" s="3">
         <v>311000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>260000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>311000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>262000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>221000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>181000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>167000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>156000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>177000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>121000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>141000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>198000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-360000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>152000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>141000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>148000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>155000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>162000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>239000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>182000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>167000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>161000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>90000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>358000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>218000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>94000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>72000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5537000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5465000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6729000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5179000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5202000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5659000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5783000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4487000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4870000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6029000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5855000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4391000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4666000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5691000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6104000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4432000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4397000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5309000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5174000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4120000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4704000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4712000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>233000</v>
+      </c>
+      <c r="E22" s="3">
         <v>248000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>225000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>240000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>222000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>171000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>123000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>115000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>109000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>106000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>109000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>117000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>106000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>143000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>136000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>157000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>100000</v>
       </c>
       <c r="T22" s="3">
         <v>100000</v>
       </c>
       <c r="U22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="V22" s="3">
         <v>108000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>111000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>131000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>138000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>129000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>272000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>133000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>244000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>115000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>116000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>96000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>122000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4592000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4496000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5802000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4233000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4288000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4835000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4997000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3650000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4071000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5239000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5035000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3564000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3877000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4877000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5297000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3461000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3498000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4532000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4343000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3278000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3916000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3940000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1003000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1246000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>841000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>864000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>876000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1034000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>592000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>704000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>997000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>909000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>656000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>628000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>990000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>989000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>675000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>541000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>789000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>726000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>172000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>502000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>729000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>499000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>613000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>872000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>881000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>725000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>780000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>695000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2297,198 +2345,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3780000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3493000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4556000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3392000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3424000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3959000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3963000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3058000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3367000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4242000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4126000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2908000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3249000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3887000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4308000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2786000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2957000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3743000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3617000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2776000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3216000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3211000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3398000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4450000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3312000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3328000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3863000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3868000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2979000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3287000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4153000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4042000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2832000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3204000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3788000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4211000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2730000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2853000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3653000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3528000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2681000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3129000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3133000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2582,8 +2639,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,17 +2695,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2653,18 +2713,18 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>100000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -2672,13 +2732,16 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2772,8 +2835,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2867,198 +2933,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-365000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-311000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-260000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-311000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-262000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-221000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-181000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-167000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-156000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-177000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-121000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-141000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-198000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>360000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-152000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-141000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-148000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-155000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-162000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-239000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-182000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-167000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-161000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>26000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>497000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3398000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4450000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3312000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3328000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3863000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3868000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2979000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3287000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4153000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4042000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2832000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3204000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3788000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4211000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2730000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2853000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3653000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3528000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2681000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3129000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3133000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3152,203 +3227,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3398000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4450000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3312000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3328000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3863000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3868000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2979000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3287000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4153000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4042000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2832000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3204000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3788000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4211000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2730000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2853000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3653000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3528000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2681000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3129000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3133000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3382,8 +3466,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3417,103 +3502,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6828000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7890000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9733000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8246000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7596000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6854000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6710000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7214000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8526000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11544000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10370000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10288000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10007000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11941000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13392000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16181000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15393000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6279000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9304000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4239000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2738000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3696000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2545000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3572,423 +3661,438 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>6048000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>7085000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>8421000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8708000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6124000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6334000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>5471000</v>
       </c>
       <c r="G43" s="3">
         <v>5471000</v>
       </c>
       <c r="H43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="I43" s="3">
         <v>5767000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5720000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5143000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5513000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5241000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5662000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4725000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4861000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4819000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5043000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4178000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4640000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5196000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5143000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4951000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5198000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5055000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5035000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7077000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7151000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7117000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7073000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7483000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7541000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7590000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6924000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7101000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6673000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6307000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5983000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6002000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5957000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5707000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5498000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5330000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5521000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5465000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5017000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5358000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5281000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5182000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2429000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1736000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1875000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1858000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1755000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1704000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2501000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2372000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2276000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2087000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1997000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2095000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1738000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1938000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1884000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2130000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1777000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1921000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2013000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2218000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1933000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1978000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1876000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22458000</v>
+      </c>
+      <c r="E46" s="3">
         <v>23111000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24940000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22648000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22305000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21866000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22521000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21653000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23416000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25545000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24336000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23091000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22608000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24655000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>26026000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>27987000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27140000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18917000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>21925000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22473000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22312000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>24431000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23346000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4001,23 +4105,23 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>63000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>60000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>66000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>113000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>126000</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -4031,8 +4135,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4082,198 +4186,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22027000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22132000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21636000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21909000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21564000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21167000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20593000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21195000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21323000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21357000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21392000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21686000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21103000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21416000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20876000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21542000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21314000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22153000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21788000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21271000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20993000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20822000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20590000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62760000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63218000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63876000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>64442000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>64550000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>63545000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>62226000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63379000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>64623000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63853000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63997000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64566000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64270000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>65245000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>64383000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>63693000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63451000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63978000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63607000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>64488000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>72589000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>72879000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>69144000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4367,8 +4480,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4462,103 +4578,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12353000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12248000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12079000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11830000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11369000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11077000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10876000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10868000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10729000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10661000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9944000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9964000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8797000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8796000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8614000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7478000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6655000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6675000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6738000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6863000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5779000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5555000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5360000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4652,103 +4774,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119598000</v>
+      </c>
+      <c r="E54" s="3">
         <v>120709000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122531000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120829000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119851000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117715000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>116282000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>117208000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120217000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121416000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119669000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119307000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>116778000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120112000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119899000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>120700000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>118560000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111723000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>114058000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>115095000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>121673000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>123687000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>118440000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4782,8 +4910,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4817,578 +4946,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13691000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14234000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14435000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14598000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13790000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14153000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14845000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14882000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14175000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14154000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14223000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13720000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12134000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12027000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11935000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12071000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10464000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10781000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10951000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11260000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10207000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10266000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10243000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7729000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10616000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11811000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10229000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13717000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14300000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11717000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8645000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9902000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13331000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11989000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8889000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8773000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8586000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7707000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11183000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>12701000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>9153000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9352000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9697000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8911000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>12113000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10508000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10920000</v>
+      </c>
+      <c r="E59" s="3">
         <v>11100000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10912000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10929000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10523000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10293000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10056000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9554000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10324000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10542000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10377000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10523000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11109000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11131000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10366000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9722000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9731000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10230000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9950000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9054000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9252000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>8868000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8469000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32340000</v>
+      </c>
+      <c r="E60" s="3">
         <v>35950000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37158000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35756000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>38030000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38746000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36618000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33081000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34401000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38027000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36589000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33132000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>32016000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31744000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>30008000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32976000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32896000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30164000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30253000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30011000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>28370000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31247000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>29220000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24253000</v>
+      </c>
+      <c r="E61" s="3">
         <v>23096000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24069000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24378000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22874000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>20582000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21286000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22848000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23767000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22322000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20558000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23099000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>21053000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22514000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23948000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23537000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23310000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>18985000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20161000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20395000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21359000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>21514000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20779000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12672000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12834000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13290000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13630000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13526000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13662000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14044000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14425000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16303000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16174000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16114000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16422000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16790000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>17314000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17367000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17309000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16413000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16666000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16660000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17110000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16392000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16483000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>15937000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5482,8 +5630,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5577,8 +5728,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5672,103 +5826,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>69540000</v>
+      </c>
+      <c r="E66" s="3">
         <v>72174000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74838000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74052000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>74711000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>73260000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72207000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>70619000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74739000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>76798000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73558000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72929000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70182000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>71931000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>71717000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74179000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>73020000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>66185000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>67480000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>67901000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>66601000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>69697000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66204000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5802,8 +5962,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5897,8 +6058,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5992,103 +6156,109 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>801000</v>
+      </c>
+      <c r="E70" s="3">
         <v>809000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>812000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>819000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>822000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>831000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>834000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>843000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>846000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>856000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>859000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>870000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>873000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>885000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>888000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>897000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>900000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>911000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>915000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>928000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>933000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>946000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>951000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>967000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>972000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>986000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>991000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6182,103 +6352,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>123132000</v>
+      </c>
+      <c r="E72" s="3">
         <v>121617000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>120443000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>118170000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>117082000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>115858000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>114163000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>112429000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>111645000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>110393000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>108361000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>106374000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>105674000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>104361000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>102539000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>100239000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>99474000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>98414000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>96625000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>94918000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>102103000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>101170000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>99831000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6372,8 +6548,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6467,8 +6646,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6562,103 +6744,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49257000</v>
+      </c>
+      <c r="E76" s="3">
         <v>47726000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46881000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45958000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44318000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43624000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43241000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45746000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44632000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43762000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45252000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45508000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45723000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>47296000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47294000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45624000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44640000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44627000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45663000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46266000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>54139000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53044000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>51285000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6752,203 +6940,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3685000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3398000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4450000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3312000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3328000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3863000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3868000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2979000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3287000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4153000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4042000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2832000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3204000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3788000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4211000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2730000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2853000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3653000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3528000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2681000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3129000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3133000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6982,103 +7179,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>712000</v>
+      </c>
+      <c r="E83" s="3">
         <v>721000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>702000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>706000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>692000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>653000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>663000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>722000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>690000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>684000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>711000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>710000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>683000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>671000</v>
       </c>
       <c r="Q83" s="3">
         <v>671000</v>
       </c>
       <c r="R83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="S83" s="3">
         <v>814000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>799000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>677000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>723000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>820000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>711000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>650000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>643000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>750000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>716000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>676000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>692000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>720000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>665000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>707000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7172,8 +7373,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7267,8 +7471,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7362,8 +7569,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7457,8 +7667,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7552,103 +7765,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4088000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5101000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4903000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5341000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3863000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3574000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4070000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3713000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3246000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5121000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4643000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4087000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5424000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4739000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4806000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4064000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4364000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4169000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4151000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3517000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4007000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3567000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7682,103 +7901,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-797000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-817000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-925000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-734000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-730000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-708000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-890000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-692000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-747000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-626000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-714000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-656000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-567000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-850000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-658000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-731000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-605000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-814000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-752000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-701000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7872,8 +8095,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7967,103 +8193,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-762000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-798000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-490000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-832000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-682000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-960000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-791000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-665000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-549000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-829000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-659000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-725000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-650000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5079000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>647000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>573000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>97000</v>
       </c>
       <c r="AA94" s="3">
         <v>97000</v>
       </c>
       <c r="AB94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>100000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8097,103 +8329,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2285000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2288000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2290000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2482000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-4899000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>566000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AB96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8287,8 +8523,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8382,8 +8621,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8477,289 +8719,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4269000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5945000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E101" s="3">
         <v>107000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-156000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>53000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-235000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-185000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-56000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-129000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-127000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>36000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-81000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>115000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>31000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>40000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-170000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>56000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-65000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>18000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-43000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-70000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>82000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>47000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>82000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>159000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>128000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1062000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1843000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1487000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>650000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>742000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>144000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-504000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1174000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>82000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>281000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>788000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9114000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5065000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1501000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-958000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1151000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,419 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20532000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20195000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21441000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21871000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20553000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20068000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20773000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20612000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19515000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19381000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20953000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20338000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18946000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18109000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19745000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19318000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17698000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17214000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18240000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17798000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17094000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16462000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17438000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9855000</v>
+        <v>10254000</v>
       </c>
       <c r="E9" s="3">
-        <v>10144000</v>
+        <v>9811000</v>
       </c>
       <c r="F9" s="3">
+        <v>10096000</v>
+      </c>
+      <c r="G9" s="3">
         <v>10501000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10613000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10404000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10897000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10846000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10802000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10326000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10664000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10365000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9791000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8922000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9253000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9142000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8659000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8518000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8806000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8653000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8410000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8342000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8776000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10340000</v>
+        <v>10278000</v>
       </c>
       <c r="E10" s="3">
-        <v>11297000</v>
+        <v>10384000</v>
       </c>
       <c r="F10" s="3">
+        <v>11345000</v>
+      </c>
+      <c r="G10" s="3">
         <v>11370000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9940000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9664000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9876000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9766000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8713000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9055000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10289000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9973000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9155000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9187000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10492000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10176000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9039000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8696000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9434000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9145000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8684000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8120000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8662000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>125000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>273000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1115,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1201,8 +1214,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,19 +1315,22 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>406000</v>
       </c>
       <c r="E14" s="3">
-        <v>1341000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>70000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1428000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1328,20 +1347,20 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1349,56 +1368,59 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>362000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>222000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>105000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>93000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8985000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>116000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>177000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>554000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>205000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>154000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>157000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>249000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>157000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>175000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1495,8 +1517,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1528,204 +1553,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15735000</v>
+        <v>16897000</v>
       </c>
       <c r="E17" s="3">
+        <v>15736000</v>
+      </c>
+      <c r="F17" s="3">
         <v>17008000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16104000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>16391000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15820000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15988000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15673000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15917000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15357000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15785000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15315000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15406000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14324000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14365000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14037000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14221000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>13764000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13763000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13509000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22287000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13235000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13551000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4460000</v>
+        <v>3635000</v>
       </c>
       <c r="E18" s="3">
+        <v>4459000</v>
+      </c>
+      <c r="F18" s="3">
         <v>4433000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5767000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4162000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4248000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4785000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4939000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3598000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4024000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5168000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5023000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3540000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3785000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5380000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5281000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3477000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3450000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4477000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4289000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3227000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3887000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1760,498 +1792,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>365000</v>
+        <v>455000</v>
       </c>
       <c r="E20" s="3">
+        <v>366000</v>
+      </c>
+      <c r="F20" s="3">
         <v>311000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>260000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>311000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>262000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>221000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>181000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>167000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>156000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>177000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>121000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>141000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>198000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-360000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>152000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>141000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>148000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>155000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>162000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>239000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>182000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>167000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>161000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>90000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>358000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>218000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>94000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>72000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4851000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5537000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5465000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6729000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5179000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5202000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5659000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5783000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4487000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4870000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6029000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5855000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4391000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4666000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5691000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6104000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4432000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4397000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5309000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5174000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4120000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4704000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E22" s="3">
         <v>233000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>248000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>225000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>240000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>222000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>171000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>123000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>115000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>109000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>106000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>109000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>117000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>106000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>143000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>136000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>157000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>100000</v>
       </c>
       <c r="U22" s="3">
         <v>100000</v>
       </c>
       <c r="V22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="W22" s="3">
         <v>108000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>111000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>131000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>138000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>129000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>272000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>133000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>244000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>115000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>116000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>96000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>122000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3870000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4592000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4496000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5802000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4233000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4288000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4835000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4997000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3650000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4071000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5239000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5035000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3564000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3877000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4877000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5297000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3461000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3498000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4532000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4343000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3278000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3916000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>726000</v>
+      </c>
+      <c r="E24" s="3">
         <v>812000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1003000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1246000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>841000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>864000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>876000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1034000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>592000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>704000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>997000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>909000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>656000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>628000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>990000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>989000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>675000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>541000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>789000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>726000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>172000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>502000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>729000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>499000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>613000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>872000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>881000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>725000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>780000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>695000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,204 +2396,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3144000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3780000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3493000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4556000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3392000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3424000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3959000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3963000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3058000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3367000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4242000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4126000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2908000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3249000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3887000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4308000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2786000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2957000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3743000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3617000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2776000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3216000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3062000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3685000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3398000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4450000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3312000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3328000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3863000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3868000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2979000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3287000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4153000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4042000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2832000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3788000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4211000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2730000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2853000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3653000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3528000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3129000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2642,8 +2699,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,17 +2758,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2716,18 +2776,18 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>100000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
@@ -2735,13 +2795,16 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2838,8 +2901,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2936,204 +3002,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-365000</v>
+        <v>-455000</v>
       </c>
       <c r="E32" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-311000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-260000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-311000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-262000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-221000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-181000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-167000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-156000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-177000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-121000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-141000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-198000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>360000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-152000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-141000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-148000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-155000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-162000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-239000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-182000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-167000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>26000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>497000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3062000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3685000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3398000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4450000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3312000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3328000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3863000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3868000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2979000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3287000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4153000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4042000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2832000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3788000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4211000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2730000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2853000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3653000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3528000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3129000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3230,209 +3305,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3062000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3685000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3398000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4450000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3312000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3328000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3863000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3868000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2979000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3287000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4153000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4042000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2832000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3788000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4211000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2730000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2853000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3653000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3528000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3129000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3467,8 +3551,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3503,106 +3588,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9482000</v>
+      </c>
+      <c r="E41" s="3">
         <v>6828000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7890000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9733000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8246000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7596000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6854000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6710000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7214000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8526000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11544000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10370000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10288000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10007000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11941000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13392000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16181000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15393000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6279000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9304000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4239000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2738000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3696000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3664,435 +3753,450 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>6048000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>7085000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>8421000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6118000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6124000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6334000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>5471000</v>
       </c>
       <c r="H43" s="3">
         <v>5471000</v>
       </c>
       <c r="I43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="J43" s="3">
         <v>5767000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5720000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5143000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5513000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5241000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5662000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4725000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4861000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4819000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5043000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4178000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4640000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5196000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5143000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4951000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5198000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5055000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7016000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7077000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7151000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7117000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7073000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7483000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7541000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7590000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6924000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7101000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6673000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6307000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5983000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6002000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5957000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5707000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5498000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5330000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5521000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5465000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5017000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5358000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5281000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2093000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2429000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1736000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1875000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1858000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1755000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1704000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2501000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2372000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2276000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2087000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1997000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2095000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1738000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1938000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1884000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2130000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1777000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1921000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2013000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2218000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1933000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1978000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24709000</v>
+      </c>
+      <c r="E46" s="3">
         <v>22458000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23111000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24940000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22648000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22305000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21866000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22521000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21653000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23416000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25545000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24336000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23091000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22608000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24655000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>26026000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>27987000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27140000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18917000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>21925000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22473000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22312000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>24431000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4108,23 +4212,23 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>63000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>60000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>66000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>113000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>126000</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -4138,8 +4242,8 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -4189,204 +4293,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22152000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22027000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22132000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21636000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21909000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21564000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21167000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20593000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21195000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21323000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21357000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21392000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21686000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21103000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21416000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20876000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21542000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21314000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22153000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21788000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21271000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20993000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20822000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62350000</v>
+      </c>
+      <c r="E49" s="3">
         <v>62760000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63218000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63876000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>64442000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>64550000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63545000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>62226000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63379000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>64623000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63853000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>63997000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64566000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>64270000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>65245000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>64383000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63693000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63451000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63978000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63607000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>64488000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>72589000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>72879000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4483,8 +4596,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4581,106 +4697,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13159000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12353000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12248000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12079000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11830000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11369000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11077000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10876000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10868000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10729000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10661000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9944000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9964000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8797000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8796000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8614000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7478000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6655000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6675000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6738000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6863000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5779000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5555000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4777,106 +4899,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122370000</v>
+      </c>
+      <c r="E54" s="3">
         <v>119598000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>120709000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122531000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120829000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119851000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117715000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116282000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117208000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120217000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>121416000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119669000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119307000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>116778000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>120112000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119899000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120700000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>118560000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>111723000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>114058000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>115095000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>121673000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>123687000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4911,8 +5039,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4947,596 +5076,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15364000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13691000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14234000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14435000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14598000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13790000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14153000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14845000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14882000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14175000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14154000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14223000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13720000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12134000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12027000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11935000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12071000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10464000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10781000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10951000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11260000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10207000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10266000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7191000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7729000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10616000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11811000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10229000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13717000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14300000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11717000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8645000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9902000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13331000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11989000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8889000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8773000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8586000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7707000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11183000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>12701000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9153000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9352000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9697000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8911000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>12113000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11072000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10920000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11100000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10912000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10929000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10523000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10293000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10056000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9554000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10324000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10542000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10377000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10523000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11109000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11131000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10366000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9722000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9731000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10230000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9950000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9054000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9252000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8868000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33627000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32340000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>35950000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37158000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35756000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>38030000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38746000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>36618000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33081000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34401000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38027000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>36589000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33132000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>32016000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>31744000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>30008000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32976000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32896000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30164000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30253000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30011000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>28370000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31247000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25269000</v>
+      </c>
+      <c r="E61" s="3">
         <v>24253000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23096000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24069000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24378000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22874000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20582000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21286000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22848000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23767000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22322000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20558000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23099000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21053000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22514000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23948000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23537000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23310000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>18985000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>20161000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20395000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>21359000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>21514000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12915000</v>
+      </c>
+      <c r="E62" s="3">
         <v>12672000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12834000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13290000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13630000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13526000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13662000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14044000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14425000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16303000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16174000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16114000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16422000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16790000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>17314000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17367000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17309000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16413000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16666000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16660000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17110000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16392000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16483000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5633,8 +5781,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5731,8 +5882,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5829,106 +5983,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72083000</v>
+      </c>
+      <c r="E66" s="3">
         <v>69540000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>72174000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74838000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>74052000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74711000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73260000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72207000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>70619000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74739000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>76798000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73558000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72929000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>70182000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>71931000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>71717000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74179000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>73020000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>66185000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>67480000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>67901000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>66601000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>69697000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5963,8 +6123,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6061,8 +6222,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6159,106 +6323,112 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>798000</v>
+      </c>
+      <c r="E70" s="3">
         <v>801000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>809000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>812000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>819000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>822000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>831000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>834000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>843000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>846000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>856000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>859000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>870000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>873000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>885000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>888000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>897000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>900000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>911000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>915000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>928000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>933000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>946000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>951000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>967000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>972000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>986000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>991000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6355,106 +6525,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>123811000</v>
+      </c>
+      <c r="E72" s="3">
         <v>123132000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>121617000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>120443000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>118170000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>117082000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>115858000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>114163000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>112429000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>111645000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>110393000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>108361000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>106374000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>105674000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>104361000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>102539000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>100239000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>99474000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>98414000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>96625000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>94918000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>102103000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>101170000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6551,8 +6727,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6649,8 +6828,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6747,106 +6929,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49489000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49257000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47726000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46881000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45958000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44318000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43624000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43241000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45746000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44632000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43762000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45252000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45508000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45723000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47296000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47294000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45624000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44640000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>44627000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45663000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46266000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>54139000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>53044000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6943,209 +7131,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3062000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3685000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3398000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4450000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3312000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3328000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3863000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3868000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2979000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3287000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4153000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4042000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2832000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3204000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3788000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4211000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2730000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2853000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3653000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3528000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2681000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3129000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7180,106 +7377,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>761000</v>
+      </c>
+      <c r="E83" s="3">
         <v>712000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>721000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>702000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>706000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>692000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>653000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>663000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>722000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>690000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>684000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>711000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>710000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>683000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>671000</v>
       </c>
       <c r="R83" s="3">
         <v>671000</v>
       </c>
       <c r="S83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="T83" s="3">
         <v>814000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>799000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>677000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>723000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>820000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>711000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>650000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>643000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>750000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>716000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>676000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>692000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>720000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>665000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>707000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7376,8 +7577,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7474,8 +7678,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7572,8 +7779,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7670,8 +7880,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7768,106 +7981,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5753000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4088000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5101000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4903000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5341000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3863000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3574000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4070000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3713000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3246000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5121000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4643000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4121000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4087000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5424000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4739000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4806000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4064000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4364000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4169000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4151000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3517000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4007000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7902,106 +8121,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-783000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-797000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-817000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-925000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-734000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-730000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-708000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-890000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-692000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-747000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-626000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-714000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-656000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-567000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-850000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-658000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-731000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-605000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-814000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-752000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-701000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8098,8 +8321,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8196,106 +8422,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-518000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-762000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-798000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-490000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-832000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-682000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-960000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-791000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-665000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-549000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-829000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-659000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-725000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-650000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5079000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>647000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>573000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>97000</v>
       </c>
       <c r="AB94" s="3">
         <v>97000</v>
       </c>
       <c r="AC94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>100000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8330,106 +8562,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2449000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-2285000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-2288000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2290000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2482000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-4899000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>566000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AC96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AD96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8526,8 +8762,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8624,8 +8863,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8722,298 +8964,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2499000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5945000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1032000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-119000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>107000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-156000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-235000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-185000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-129000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-127000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>36000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>115000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>31000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>40000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-170000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>56000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-65000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>18000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-43000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>82000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>47000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>82000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>159000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>128000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2653000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1843000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1487000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>650000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>742000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>144000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-504000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1174000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>82000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>281000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>788000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9114000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5065000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1501000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-958000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1151000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,431 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21737000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20532000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20195000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21441000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21871000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20553000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20068000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20773000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20612000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19515000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19381000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20953000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20338000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18946000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18109000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19745000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19318000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17698000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17214000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18240000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17798000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17094000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16462000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10380000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10254000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9811000</v>
       </c>
-      <c r="F9" s="3">
-        <v>10096000</v>
-      </c>
       <c r="G9" s="3">
+        <v>10144000</v>
+      </c>
+      <c r="H9" s="3">
         <v>10501000</v>
       </c>
-      <c r="H9" s="3">
-        <v>10613000</v>
-      </c>
       <c r="I9" s="3">
+        <v>10453000</v>
+      </c>
+      <c r="J9" s="3">
         <v>10404000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10897000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10846000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10802000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10326000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10664000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10365000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9791000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8922000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9253000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9142000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8659000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8518000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8806000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8653000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8410000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8342000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11357000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10278000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10384000</v>
       </c>
-      <c r="F10" s="3">
-        <v>11345000</v>
-      </c>
       <c r="G10" s="3">
+        <v>11297000</v>
+      </c>
+      <c r="H10" s="3">
         <v>11370000</v>
       </c>
-      <c r="H10" s="3">
-        <v>9940000</v>
-      </c>
       <c r="I10" s="3">
+        <v>10100000</v>
+      </c>
+      <c r="J10" s="3">
         <v>9664000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9876000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9766000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8713000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9055000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10289000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9973000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9155000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9187000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10492000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10176000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9039000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>8696000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9434000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9145000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8684000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8120000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>125000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>273000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1116,16 +1128,17 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>2000000</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1136,8 +1149,8 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
+      <c r="I12" s="3">
+        <v>2000000</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1217,8 +1230,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,28 +1334,31 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>406000</v>
+        <v>886000</v>
       </c>
       <c r="E14" s="3">
+        <v>413000</v>
+      </c>
+      <c r="F14" s="3">
         <v>70000</v>
       </c>
-      <c r="F14" s="3">
-        <v>1428000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
+      <c r="G14" s="3">
+        <v>1341000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>338000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1350,20 +1369,20 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1371,79 +1390,82 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>362000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>222000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>105000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>93000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8985000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>116000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>177000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>554000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>205000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>154000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>157000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>249000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>157000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>175000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>728000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>761000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>712000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>721000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>702000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>706000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>692000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1520,8 +1542,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1554,210 +1579,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16897000</v>
+        <v>15702000</v>
       </c>
       <c r="E17" s="3">
-        <v>15736000</v>
+        <v>16139000</v>
       </c>
       <c r="F17" s="3">
-        <v>17008000</v>
+        <v>15562000</v>
       </c>
       <c r="G17" s="3">
-        <v>16104000</v>
+        <v>15562000</v>
       </c>
       <c r="H17" s="3">
-        <v>16391000</v>
+        <v>16006000</v>
       </c>
       <c r="I17" s="3">
-        <v>15820000</v>
+        <v>15731000</v>
       </c>
       <c r="J17" s="3">
+        <v>15734000</v>
+      </c>
+      <c r="K17" s="3">
         <v>15988000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15673000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15917000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15357000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15785000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15315000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15406000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14324000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14365000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14037000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14221000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13764000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13763000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13509000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22287000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13235000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3635000</v>
+        <v>6035000</v>
       </c>
       <c r="E18" s="3">
-        <v>4459000</v>
+        <v>4393000</v>
       </c>
       <c r="F18" s="3">
-        <v>4433000</v>
+        <v>4633000</v>
       </c>
       <c r="G18" s="3">
-        <v>5767000</v>
+        <v>5879000</v>
       </c>
       <c r="H18" s="3">
-        <v>4162000</v>
+        <v>5865000</v>
       </c>
       <c r="I18" s="3">
-        <v>4248000</v>
+        <v>4822000</v>
       </c>
       <c r="J18" s="3">
+        <v>4334000</v>
+      </c>
+      <c r="K18" s="3">
         <v>4785000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4939000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3598000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4024000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5168000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5023000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3540000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3785000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5380000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5281000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3477000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3450000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4477000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4289000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3227000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1793,513 +1825,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>455000</v>
+        <v>-93000</v>
       </c>
       <c r="E20" s="3">
-        <v>366000</v>
+        <v>-3000</v>
       </c>
       <c r="F20" s="3">
-        <v>311000</v>
+        <v>-159000</v>
       </c>
       <c r="G20" s="3">
-        <v>260000</v>
+        <v>-73000</v>
       </c>
       <c r="H20" s="3">
-        <v>311000</v>
+        <v>-34000</v>
       </c>
       <c r="I20" s="3">
-        <v>262000</v>
+        <v>127000</v>
       </c>
       <c r="J20" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="K20" s="3">
         <v>221000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>181000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>167000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>156000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>177000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>121000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>141000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>198000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-360000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>152000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>141000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>148000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>155000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>162000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>239000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>182000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>167000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>161000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>90000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>358000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>218000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>94000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>72000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4851000</v>
+        <v>6856000</v>
       </c>
       <c r="E21" s="3">
-        <v>5537000</v>
+        <v>5157000</v>
       </c>
       <c r="F21" s="3">
-        <v>5465000</v>
+        <v>5504000</v>
       </c>
       <c r="G21" s="3">
-        <v>6729000</v>
+        <v>6673000</v>
       </c>
       <c r="H21" s="3">
-        <v>5179000</v>
+        <v>6601000</v>
       </c>
       <c r="I21" s="3">
-        <v>5202000</v>
+        <v>5401000</v>
       </c>
       <c r="J21" s="3">
+        <v>5119000</v>
+      </c>
+      <c r="K21" s="3">
         <v>5659000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5783000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4487000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4870000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6029000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5855000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4391000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4666000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5691000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6104000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4432000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4397000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5309000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5174000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4120000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E22" s="3">
         <v>220000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>233000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>248000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>225000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>222000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>171000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>123000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>115000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>109000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>106000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>109000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>117000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>106000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>143000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>136000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>157000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>100000</v>
       </c>
       <c r="V22" s="3">
         <v>100000</v>
       </c>
       <c r="W22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="X22" s="3">
         <v>108000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>111000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>131000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>138000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>129000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>272000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>133000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>244000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>115000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>116000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>96000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>122000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5139000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3870000</v>
       </c>
-      <c r="E23" s="3">
-        <v>4592000</v>
-      </c>
       <c r="F23" s="3">
+        <v>4593000</v>
+      </c>
+      <c r="G23" s="3">
         <v>4496000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5802000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4233000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4288000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4835000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4997000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3650000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4071000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5239000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5035000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3564000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3877000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4877000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5297000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3461000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3498000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4532000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4343000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3278000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1152000</v>
+      </c>
+      <c r="E24" s="3">
         <v>726000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>812000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1003000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1246000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>841000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>864000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>876000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1034000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>592000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>704000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>997000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>909000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>656000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>628000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>990000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>989000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>675000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>541000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>789000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>726000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>172000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>502000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>729000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>499000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>613000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>872000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>881000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>725000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>780000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>695000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,210 +2447,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3987000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3144000</v>
       </c>
-      <c r="E26" s="3">
-        <v>3780000</v>
-      </c>
       <c r="F26" s="3">
+        <v>3781000</v>
+      </c>
+      <c r="G26" s="3">
         <v>3493000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4556000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3392000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3424000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3959000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3963000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3058000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3367000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4242000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4126000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2908000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3249000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3887000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4308000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2786000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2957000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3743000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3617000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2776000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3887000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3062000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3685000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3398000</v>
       </c>
-      <c r="G27" s="3">
-        <v>4450000</v>
-      </c>
       <c r="H27" s="3">
+        <v>4451000</v>
+      </c>
+      <c r="I27" s="3">
         <v>3312000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3328000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3863000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3868000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2979000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3287000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4153000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4042000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2832000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3204000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3788000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4211000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2730000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2853000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3653000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3528000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2681000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2702,8 +2759,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2761,17 +2821,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2779,18 +2839,18 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>100000</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
@@ -2798,13 +2858,16 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2904,8 +2967,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3005,210 +3071,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-455000</v>
+        <v>93000</v>
       </c>
       <c r="E32" s="3">
-        <v>-366000</v>
+        <v>3000</v>
       </c>
       <c r="F32" s="3">
-        <v>-311000</v>
+        <v>159000</v>
       </c>
       <c r="G32" s="3">
-        <v>-260000</v>
+        <v>73000</v>
       </c>
       <c r="H32" s="3">
-        <v>-311000</v>
+        <v>34000</v>
       </c>
       <c r="I32" s="3">
-        <v>-262000</v>
+        <v>-127000</v>
       </c>
       <c r="J32" s="3">
+        <v>93000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-221000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-181000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-167000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-156000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-177000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-121000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-141000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-198000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>360000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-152000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-141000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-148000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-155000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-162000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-239000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-182000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>26000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>497000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3062000</v>
+        <v>3959000</v>
       </c>
       <c r="E33" s="3">
-        <v>3685000</v>
+        <v>3137000</v>
       </c>
       <c r="F33" s="3">
-        <v>3398000</v>
+        <v>3754000</v>
       </c>
       <c r="G33" s="3">
-        <v>4450000</v>
+        <v>3468000</v>
       </c>
       <c r="H33" s="3">
-        <v>3312000</v>
+        <v>4521000</v>
       </c>
       <c r="I33" s="3">
-        <v>3328000</v>
+        <v>3384000</v>
       </c>
       <c r="J33" s="3">
+        <v>3397000</v>
+      </c>
+      <c r="K33" s="3">
         <v>3863000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3868000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2979000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3287000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4153000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4042000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2832000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3204000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3788000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4211000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2730000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2853000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3653000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3528000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2681000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3308,215 +3383,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3062000</v>
+        <v>3959000</v>
       </c>
       <c r="E35" s="3">
-        <v>3685000</v>
+        <v>3137000</v>
       </c>
       <c r="F35" s="3">
-        <v>3398000</v>
+        <v>3754000</v>
       </c>
       <c r="G35" s="3">
-        <v>4450000</v>
+        <v>3468000</v>
       </c>
       <c r="H35" s="3">
-        <v>3312000</v>
+        <v>4521000</v>
       </c>
       <c r="I35" s="3">
-        <v>3328000</v>
+        <v>3384000</v>
       </c>
       <c r="J35" s="3">
+        <v>3397000</v>
+      </c>
+      <c r="K35" s="3">
         <v>3863000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3868000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2979000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3287000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4153000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4042000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2832000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3204000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3788000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4211000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2730000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2853000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3653000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3528000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2681000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3552,8 +3636,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3589,109 +3674,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12156000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9482000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6828000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7890000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9733000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8246000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7596000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6854000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6710000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7214000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8526000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11544000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10370000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10288000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10007000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11941000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13392000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16181000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15393000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6279000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9304000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4239000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2738000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3756,447 +3845,462 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>6048000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>7085000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6314000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6118000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6124000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6334000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>5471000</v>
       </c>
       <c r="I43" s="3">
         <v>5471000</v>
       </c>
       <c r="J43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="K43" s="3">
         <v>5767000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5720000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5143000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5513000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5241000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5662000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4725000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4861000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4819000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5043000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4178000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4640000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5196000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5143000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4951000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5198000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7287000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7016000</v>
       </c>
-      <c r="E44" s="3">
-        <v>7077000</v>
-      </c>
       <c r="F44" s="3">
-        <v>7151000</v>
+        <v>7078000</v>
       </c>
       <c r="G44" s="3">
+        <v>7152000</v>
+      </c>
+      <c r="H44" s="3">
         <v>7117000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7073000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7483000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7541000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7590000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6924000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7101000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6673000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6307000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5983000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6002000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5957000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5707000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5498000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5330000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5521000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5465000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5017000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5358000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2093000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2429000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1736000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1875000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1858000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1755000</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>1704000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2501000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2372000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2276000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2087000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1997000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2095000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1738000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1938000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1884000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2130000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1777000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1921000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2013000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2218000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1933000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27449000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24709000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22458000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23111000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24940000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22648000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22305000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21866000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22521000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21653000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23416000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25545000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24336000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23091000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22608000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24655000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>26026000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>27987000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>27140000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18917000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>21925000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22473000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>22312000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4215,23 +4319,23 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>63000</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
+        <v>91000</v>
+      </c>
+      <c r="K47" s="3">
         <v>60000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>66000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>113000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>126000</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -4245,8 +4349,8 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4296,210 +4400,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22152000</v>
+        <v>22506000</v>
       </c>
       <c r="E48" s="3">
+        <v>23027000</v>
+      </c>
+      <c r="F48" s="3">
         <v>22027000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22132000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21636000</v>
       </c>
-      <c r="H48" s="3">
-        <v>21909000</v>
-      </c>
       <c r="I48" s="3">
+        <v>22690000</v>
+      </c>
+      <c r="J48" s="3">
         <v>21564000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21167000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20593000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21195000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21323000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21357000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21392000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21686000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21103000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21416000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20876000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21542000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21314000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>22153000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21788000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21271000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20993000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>63023000</v>
+      </c>
+      <c r="E49" s="3">
         <v>62350000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>62760000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63218000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63876000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>64442000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>64550000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63545000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>62226000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63379000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>64623000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>63853000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>63997000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>64566000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>64270000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>65245000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>64383000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63693000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63451000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63978000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>63607000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>64488000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>72589000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4712,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4700,109 +4816,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13159000</v>
+        <v>13504000</v>
       </c>
       <c r="E52" s="3">
+        <v>12284000</v>
+      </c>
+      <c r="F52" s="3">
         <v>12353000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12248000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12079000</v>
       </c>
-      <c r="H52" s="3">
-        <v>11830000</v>
-      </c>
       <c r="I52" s="3">
-        <v>11369000</v>
+        <v>11049000</v>
       </c>
       <c r="J52" s="3">
+        <v>11341000</v>
+      </c>
+      <c r="K52" s="3">
         <v>11077000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10876000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10868000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10729000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10661000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9944000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9964000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8797000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8796000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8614000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7478000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6655000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6675000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6738000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6863000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5779000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4902,109 +5024,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>126482000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122370000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119598000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>120709000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122531000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120829000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119851000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>117715000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>116282000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>117208000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120217000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>121416000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119669000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119307000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>116778000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>120112000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>119899000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120700000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>118560000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>111723000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>114058000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>115095000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>121673000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5040,8 +5168,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5077,614 +5206,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15350000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15364000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13691000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14234000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14435000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14598000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13790000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14153000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14845000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14882000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14175000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14154000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14223000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13720000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12134000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12027000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11935000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12071000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10464000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10781000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10951000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11260000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10207000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7191000</v>
+        <v>10409000</v>
       </c>
       <c r="E58" s="3">
+        <v>7465000</v>
+      </c>
+      <c r="F58" s="3">
         <v>7729000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10616000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11811000</v>
       </c>
-      <c r="H58" s="3">
-        <v>10229000</v>
-      </c>
       <c r="I58" s="3">
+        <v>11082000</v>
+      </c>
+      <c r="J58" s="3">
         <v>13717000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14300000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11717000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8645000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9902000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13331000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11989000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8889000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8773000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8586000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7707000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11183000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>12701000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9153000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9352000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9697000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8911000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>11072000</v>
+      <c r="D59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>10920000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>11100000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>10912000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>10929000</v>
+        <v>4183000</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I59" s="3">
+        <v>3917000</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
+        <v>10293000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>10056000</v>
+      </c>
+      <c r="M59" s="3">
+        <v>9554000</v>
+      </c>
+      <c r="N59" s="3">
+        <v>10324000</v>
+      </c>
+      <c r="O59" s="3">
+        <v>10542000</v>
+      </c>
+      <c r="P59" s="3">
+        <v>10377000</v>
+      </c>
+      <c r="Q59" s="3">
         <v>10523000</v>
       </c>
-      <c r="J59" s="3">
-        <v>10293000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>10056000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>9554000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>10324000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>10542000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>10377000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>10523000</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11109000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11131000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10366000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9722000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9731000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10230000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9950000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9054000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9252000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36420000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33627000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32340000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35950000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37158000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35756000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38030000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38746000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36618000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33081000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34401000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38027000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36589000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33132000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>32016000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>31744000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>30008000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32976000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32896000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30164000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30253000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30011000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>28370000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25269000</v>
+        <v>25744000</v>
       </c>
       <c r="E61" s="3">
+        <v>26260000</v>
+      </c>
+      <c r="F61" s="3">
         <v>24253000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>23096000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24069000</v>
       </c>
-      <c r="H61" s="3">
-        <v>24378000</v>
-      </c>
       <c r="I61" s="3">
+        <v>25418000</v>
+      </c>
+      <c r="J61" s="3">
         <v>22874000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20582000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21286000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22848000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23767000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22322000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20558000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23099000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21053000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22514000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23948000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23537000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23310000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>18985000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>20161000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20395000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>21359000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12915000</v>
+        <v>5758000</v>
       </c>
       <c r="E62" s="3">
-        <v>12672000</v>
+        <v>1872000</v>
       </c>
       <c r="F62" s="3">
-        <v>12834000</v>
+        <v>6388000</v>
       </c>
       <c r="G62" s="3">
-        <v>13290000</v>
+        <v>6616000</v>
       </c>
       <c r="H62" s="3">
-        <v>13630000</v>
+        <v>6477000</v>
       </c>
       <c r="I62" s="3">
-        <v>13526000</v>
+        <v>2306000</v>
       </c>
       <c r="J62" s="3">
+        <v>7104000</v>
+      </c>
+      <c r="K62" s="3">
         <v>13662000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14044000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14425000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16303000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16174000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16114000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16422000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16790000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>17314000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17367000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17309000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16413000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16666000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16660000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17110000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16392000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5784,8 +5932,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5885,8 +6036,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5986,109 +6140,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>72083000</v>
+        <v>74342000</v>
       </c>
       <c r="E66" s="3">
-        <v>69540000</v>
+        <v>71812000</v>
       </c>
       <c r="F66" s="3">
-        <v>72174000</v>
+        <v>69265000</v>
       </c>
       <c r="G66" s="3">
-        <v>74838000</v>
+        <v>71881000</v>
       </c>
       <c r="H66" s="3">
-        <v>74052000</v>
+        <v>74518000</v>
       </c>
       <c r="I66" s="3">
-        <v>74711000</v>
+        <v>73764000</v>
       </c>
       <c r="J66" s="3">
+        <v>74430000</v>
+      </c>
+      <c r="K66" s="3">
         <v>73260000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72207000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>70619000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74739000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76798000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73558000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72929000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70182000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>71931000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>71717000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>74179000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>73020000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>66185000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>67480000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>67901000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66601000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6124,8 +6284,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6225,8 +6386,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6326,109 +6490,115 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>791000</v>
+      </c>
+      <c r="E70" s="3">
         <v>798000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>801000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>809000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>812000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>819000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>822000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>831000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>834000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>843000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>846000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>856000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>859000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>870000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>873000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>885000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>888000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>897000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>900000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>911000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>915000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>928000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>933000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>946000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>951000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>967000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>972000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>986000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>991000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6528,109 +6698,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>125361000</v>
+      </c>
+      <c r="E72" s="3">
         <v>123811000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>123132000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>121617000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>120443000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>118170000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>117082000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115858000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>114163000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>112429000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>111645000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>110393000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>108361000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>106374000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>105674000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>104361000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>102539000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>100239000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>99474000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>98414000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>96625000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>94918000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>102103000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6730,8 +6906,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6831,8 +7010,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6932,109 +7114,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>49489000</v>
+        <v>51049000</v>
       </c>
       <c r="E76" s="3">
+        <v>49488000</v>
+      </c>
+      <c r="F76" s="3">
         <v>49257000</v>
       </c>
-      <c r="F76" s="3">
-        <v>47726000</v>
-      </c>
       <c r="G76" s="3">
-        <v>46881000</v>
+        <v>47725000</v>
       </c>
       <c r="H76" s="3">
+        <v>46880000</v>
+      </c>
+      <c r="I76" s="3">
         <v>45958000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44318000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43624000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43241000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>45746000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44632000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43762000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45252000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45508000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45723000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>47296000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>47294000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45624000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>44640000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44627000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45663000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46266000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>54139000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7134,215 +7322,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3062000</v>
+        <v>3959000</v>
       </c>
       <c r="E81" s="3">
-        <v>3685000</v>
+        <v>3137000</v>
       </c>
       <c r="F81" s="3">
-        <v>3398000</v>
+        <v>3754000</v>
       </c>
       <c r="G81" s="3">
-        <v>4450000</v>
+        <v>3468000</v>
       </c>
       <c r="H81" s="3">
-        <v>3312000</v>
+        <v>4521000</v>
       </c>
       <c r="I81" s="3">
-        <v>3328000</v>
+        <v>3384000</v>
       </c>
       <c r="J81" s="3">
+        <v>3397000</v>
+      </c>
+      <c r="K81" s="3">
         <v>3863000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3868000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2979000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3287000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4153000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4042000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2832000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3204000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3788000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4211000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2730000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2853000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3653000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3528000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2681000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7378,109 +7575,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>761000</v>
+        <v>615000</v>
       </c>
       <c r="E83" s="3">
-        <v>712000</v>
+        <v>620000</v>
       </c>
       <c r="F83" s="3">
-        <v>721000</v>
+        <v>610000</v>
       </c>
       <c r="G83" s="3">
-        <v>702000</v>
+        <v>574000</v>
       </c>
       <c r="H83" s="3">
-        <v>706000</v>
+        <v>583000</v>
       </c>
       <c r="I83" s="3">
-        <v>692000</v>
+        <v>640000</v>
       </c>
       <c r="J83" s="3">
+        <v>611000</v>
+      </c>
+      <c r="K83" s="3">
         <v>653000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>663000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>722000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>690000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>684000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>711000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>710000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>683000</v>
-      </c>
-      <c r="R83" s="3">
-        <v>671000</v>
       </c>
       <c r="S83" s="3">
         <v>671000</v>
       </c>
       <c r="T83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="U83" s="3">
         <v>814000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>799000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>677000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>723000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>820000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>711000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>650000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>643000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>750000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>716000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>676000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>692000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>720000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>665000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>707000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7580,8 +7781,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7681,8 +7885,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7782,8 +7989,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7883,8 +8093,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7984,109 +8197,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5753000</v>
+        <v>4302000</v>
       </c>
       <c r="E89" s="3">
+        <v>5754000</v>
+      </c>
+      <c r="F89" s="3">
         <v>4088000</v>
       </c>
-      <c r="F89" s="3">
-        <v>5101000</v>
-      </c>
       <c r="G89" s="3">
-        <v>4903000</v>
+        <v>5100000</v>
       </c>
       <c r="H89" s="3">
+        <v>4904000</v>
+      </c>
+      <c r="I89" s="3">
         <v>5341000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3863000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3574000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4070000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3713000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3246000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5121000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4643000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4087000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5424000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4739000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4806000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4064000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4364000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4169000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4151000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3517000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8122,109 +8341,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-993000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-783000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-797000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-817000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-925000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-734000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-730000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-708000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-890000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-692000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-747000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-626000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-714000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-656000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-567000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-850000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-658000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-731000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-605000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-814000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-752000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8324,8 +8547,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8425,109 +8651,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1108000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-518000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-762000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-798000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-490000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-832000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-682000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-960000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-791000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-665000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-549000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-829000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-659000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-725000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-650000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5079000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>647000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>573000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>97000</v>
       </c>
       <c r="AC94" s="3">
         <v>97000</v>
       </c>
       <c r="AD94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>100000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8563,109 +8795,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-2449000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-2285000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-2288000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-2290000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-2482000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-4899000</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>566000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AD96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8765,8 +9001,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8866,8 +9105,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8967,307 +9209,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-634000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5945000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-83000</v>
+        <v>-156000</v>
       </c>
       <c r="E101" s="3">
-        <v>-119000</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>107000</v>
+        <v>12000</v>
       </c>
       <c r="G101" s="3">
-        <v>-156000</v>
+        <v>53000</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-235000</v>
       </c>
       <c r="I101" s="3">
-        <v>12000</v>
+        <v>-185000</v>
       </c>
       <c r="J101" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="K101" s="3">
         <v>53000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-235000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-185000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-56000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-129000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-127000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>36000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-81000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>115000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>31000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>40000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-170000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>56000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-65000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>18000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>82000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>47000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>82000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>159000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>128000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2653000</v>
+        <v>2676000</v>
       </c>
       <c r="E102" s="3">
+        <v>2654000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-1843000</v>
-      </c>
       <c r="G102" s="3">
-        <v>1487000</v>
+        <v>-1844000</v>
       </c>
       <c r="H102" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="I102" s="3">
         <v>650000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>742000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>144000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-504000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1174000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>82000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>281000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>788000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9114000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5065000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1501000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-958000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21882000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21737000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20532000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20195000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21441000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21871000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20553000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20068000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20773000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20612000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19515000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19381000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20953000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20338000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18946000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18109000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19745000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19318000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17698000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17214000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18240000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17798000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17094000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10390000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10380000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10254000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9811000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10144000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10501000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10453000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10404000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10897000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10846000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10802000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10326000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10664000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10365000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9791000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8922000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9253000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9142000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8659000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8518000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8806000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8653000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8410000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11492000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11357000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10278000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10384000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11297000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11370000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10100000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9664000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9876000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9766000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8713000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9055000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10289000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9973000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9155000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9187000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10492000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10176000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9039000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8696000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9434000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9145000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8684000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>125000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>273000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1129,19 +1141,20 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1149,11 +1162,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1233,8 +1246,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1337,31 +1353,34 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E14" s="3">
         <v>886000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>413000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>70000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1341000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>338000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1372,20 +1391,20 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1393,83 +1412,86 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>362000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>222000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>105000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>93000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8985000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>116000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>177000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>554000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>205000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>154000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>157000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>249000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>157000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>175000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>706000</v>
+      </c>
+      <c r="E15" s="3">
         <v>728000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>761000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>712000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>721000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>702000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>706000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>692000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1545,8 +1567,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1580,216 +1605,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15934000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15702000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16139000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>15562000</v>
       </c>
       <c r="G17" s="3">
         <v>15562000</v>
       </c>
       <c r="H17" s="3">
+        <v>15562000</v>
+      </c>
+      <c r="I17" s="3">
         <v>16006000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15731000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15734000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15988000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15673000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15917000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15357000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15785000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15315000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15406000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14324000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14365000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14037000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14221000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>13764000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13763000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13509000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22287000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5948000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6035000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4393000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4633000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5879000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5865000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4822000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4334000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4785000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4939000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3598000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4024000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5168000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5023000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3540000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3785000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5380000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5281000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3477000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3450000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4477000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4289000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1826,528 +1858,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-93000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-159000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-73000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-34000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>127000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-93000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>221000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>181000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>167000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>156000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>177000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>121000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>141000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>198000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-360000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>152000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>141000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>148000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>155000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>162000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>239000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>182000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>167000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>161000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>90000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>358000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>218000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>94000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>72000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6721000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6856000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5157000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5504000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6673000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6601000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5401000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5119000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5659000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5783000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4487000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4870000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6029000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5855000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4391000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4666000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5691000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6104000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4432000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4397000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5309000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5174000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>240000</v>
+      </c>
+      <c r="E22" s="3">
         <v>238000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>220000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>233000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>248000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>225000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>240000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>222000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>171000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>123000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>115000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>109000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>106000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>109000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>117000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>106000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>143000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>136000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>157000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>100000</v>
       </c>
       <c r="W22" s="3">
         <v>100000</v>
       </c>
       <c r="X22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>108000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>111000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>131000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>138000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>129000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>272000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>133000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>244000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>115000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>116000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>96000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5846000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5139000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3870000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4593000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4496000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5802000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4233000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4288000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4835000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4997000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3650000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4071000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5239000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5035000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3564000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3877000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4877000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5297000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3461000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3498000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4532000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4343000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1187000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1152000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>726000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>812000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1003000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1246000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>841000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>864000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>876000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1034000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>592000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>704000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>997000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>909000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>656000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>628000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>990000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>989000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>675000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>541000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>789000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>726000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>172000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>502000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>729000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>499000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>613000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>872000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>881000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>725000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>780000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>695000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2450,216 +2498,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4659000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3987000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3144000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3781000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3493000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4556000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3392000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3424000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3959000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3963000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3058000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3367000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4242000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4126000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2908000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3249000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3887000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4308000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2786000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2957000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3743000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3617000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4558000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3887000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3062000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3685000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3398000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4451000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3312000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3328000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3863000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3868000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2979000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3287000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4153000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4042000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2832000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3204000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3788000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4211000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2730000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2853000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3653000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3528000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2762,8 +2819,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2824,17 +2884,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2842,18 +2902,18 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>100000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
@@ -2861,13 +2921,16 @@
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2970,8 +3033,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3074,216 +3140,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E32" s="3">
         <v>93000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>159000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>73000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>34000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-127000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>93000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-221000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-181000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-167000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-156000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-177000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-121000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-141000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-198000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>360000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-152000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-141000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-148000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-155000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-162000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-239000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>26000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>497000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4630000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3959000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3137000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3754000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3468000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4521000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3384000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3397000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3863000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3868000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2979000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3287000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4153000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4042000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2832000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3204000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3788000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4211000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2730000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2853000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3653000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3528000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3386,221 +3461,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4630000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3959000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3137000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3754000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3468000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4521000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3384000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3397000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3863000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3868000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2979000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3287000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4153000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4042000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2832000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3204000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3788000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4211000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2730000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2853000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3653000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3528000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3637,8 +3721,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3675,112 +3760,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10230000</v>
+      </c>
+      <c r="E41" s="3">
         <v>12156000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9482000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6828000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7890000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9733000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8246000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7596000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6854000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6710000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7214000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8526000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11544000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10370000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10288000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10007000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11941000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13392000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16181000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>15393000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6279000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9304000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4239000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3848,251 +3937,260 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>6048000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6234000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6314000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6118000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6124000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6334000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>5471000</v>
       </c>
       <c r="J43" s="3">
         <v>5471000</v>
       </c>
       <c r="K43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="L43" s="3">
         <v>5767000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5720000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5143000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5513000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5241000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5662000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4725000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4861000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4819000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5043000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4178000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4640000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5196000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5143000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4951000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7020000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7287000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7016000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7078000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7152000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7117000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7073000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7483000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7541000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7590000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6924000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7101000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6673000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6307000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5983000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6002000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5957000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5707000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5498000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5330000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5521000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5465000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5017000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4117,190 +4215,196 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>1704000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2501000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2372000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2276000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2087000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1997000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2095000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1738000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1938000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1884000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2130000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1777000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1921000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2013000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2218000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25642000</v>
+      </c>
+      <c r="E46" s="3">
         <v>27449000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>24709000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22458000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23111000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24940000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22648000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22305000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21866000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22521000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21653000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23416000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>25545000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24336000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>23091000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22608000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>24655000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>26026000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>27987000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27140000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18917000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>21925000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>22473000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4322,23 +4426,23 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>91000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>60000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>66000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>113000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>126000</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>8</v>
@@ -4352,8 +4456,8 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -4403,216 +4507,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22074000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22506000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23027000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22027000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22132000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21636000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22690000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21564000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21167000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20593000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21195000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21323000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21357000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21392000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21686000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21103000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21416000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20876000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21542000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21314000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>22153000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21788000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21271000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>61731000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63023000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>62350000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>62760000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>63218000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>63876000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>64442000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>64550000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63545000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>62226000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63379000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64623000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>63853000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>63997000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>64566000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>64270000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>65245000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>64383000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63693000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63451000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>63978000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>63607000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>64488000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4715,8 +4828,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4819,112 +4935,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13192000</v>
+      </c>
+      <c r="E52" s="3">
         <v>13504000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12284000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12353000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12248000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12079000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11049000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11341000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11077000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10876000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10868000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10729000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10661000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9944000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9964000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8797000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8796000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8614000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7478000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6655000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6675000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6738000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6863000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5027,112 +5149,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122639000</v>
+      </c>
+      <c r="E54" s="3">
         <v>126482000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122370000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>119598000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>120709000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122531000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120829000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119851000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117715000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116282000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117208000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120217000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>121416000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>119669000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119307000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>116778000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120112000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>119899000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>120700000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>118560000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>111723000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>114058000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>115095000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5169,8 +5297,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5207,227 +5336,234 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14495000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15350000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15364000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13691000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14234000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14435000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14598000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13790000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14153000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14845000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14882000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14175000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14154000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14223000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13720000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12134000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12027000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11935000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12071000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>10464000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10781000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10951000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11260000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9424000</v>
+      </c>
+      <c r="E58" s="3">
         <v>10409000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7465000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7729000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10616000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11811000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11082000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13717000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14300000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11717000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8645000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9902000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13331000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11989000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8889000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8773000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8586000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>7707000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11183000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>12701000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9153000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9352000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>9697000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -5435,404 +5571,416 @@
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>3917000</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10293000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10056000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9554000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10324000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10542000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10377000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10523000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11109000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11131000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10366000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9722000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9731000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10230000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9950000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9054000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33797000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36420000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33627000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32340000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>35950000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37158000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35756000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38030000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38746000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>36618000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33081000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>34401000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38027000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36589000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33132000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>32016000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>31744000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30008000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>32976000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32896000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30164000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30253000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30011000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25263000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25744000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26260000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24253000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23096000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24069000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25418000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>22874000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20582000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>21286000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>22848000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>23767000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22322000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20558000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>23099000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21053000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22514000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>23948000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23537000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23310000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>18985000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>20161000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20395000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5411000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5758000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1872000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6388000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6616000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6477000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2306000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7104000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13662000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14044000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14425000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16303000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16174000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16114000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16422000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16790000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>17314000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17367000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17309000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16413000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16666000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16660000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17110000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5935,8 +6083,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6039,8 +6190,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6143,112 +6297,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71196000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74342000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71812000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>69265000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71881000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74518000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>73764000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74430000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73260000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>72207000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>70619000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74739000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>76798000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>73558000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72929000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70182000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>71931000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>71717000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>74179000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>73020000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>66185000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>67480000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>67901000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6285,8 +6445,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6389,8 +6550,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6493,112 +6657,118 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>788000</v>
+      </c>
+      <c r="E70" s="3">
         <v>791000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>798000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>801000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>809000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>812000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>819000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>822000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>831000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>834000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>843000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>846000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>856000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>859000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>870000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>873000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>885000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>888000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>897000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>900000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>911000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>915000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>928000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>933000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>946000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>951000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>967000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>972000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>986000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>991000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6701,112 +6871,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>127544000</v>
+      </c>
+      <c r="E72" s="3">
         <v>125361000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>123811000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>123132000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>121617000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>120443000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>118170000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>117082000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>115858000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>114163000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>112429000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>111645000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>110393000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>108361000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>106374000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>105674000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>104361000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>102539000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>100239000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>99474000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>98414000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>96625000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>94918000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6909,8 +7085,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7013,8 +7192,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7117,112 +7299,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50380000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51049000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49488000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49257000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47725000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46880000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>45958000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44318000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43624000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43241000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45746000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44632000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43762000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>45252000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45508000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45723000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>47296000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>47294000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45624000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44640000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>44627000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>45663000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>46266000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7325,221 +7513,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4630000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3959000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3137000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3754000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3468000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4521000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3384000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3397000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3863000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3868000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2979000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3287000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4153000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4042000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2832000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3204000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3788000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4211000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2730000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2853000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3653000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3528000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7576,112 +7773,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E83" s="3">
         <v>615000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>620000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>610000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>574000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>583000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>640000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>611000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>653000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>663000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>722000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>690000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>684000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>711000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>710000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>683000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>671000</v>
       </c>
       <c r="T83" s="3">
         <v>671000</v>
       </c>
       <c r="U83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="V83" s="3">
         <v>814000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>799000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>677000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>723000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>820000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>711000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>650000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>643000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>750000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>716000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>676000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>692000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>720000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>665000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>707000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7784,8 +7985,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7888,8 +8092,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7992,8 +8199,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8096,8 +8306,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8200,112 +8413,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4825000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4302000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5754000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4088000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5100000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4904000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5341000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3863000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3574000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4070000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3713000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3246000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5121000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4643000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4121000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4087000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5424000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4739000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4806000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4064000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4364000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4169000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4151000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8342,112 +8561,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-925000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-993000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-783000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-797000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-817000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-925000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-734000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-730000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-708000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-890000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-692000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-747000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-626000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-714000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-656000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-567000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-850000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-658000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-731000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-605000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-814000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8550,8 +8773,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8654,112 +8880,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-921000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-518000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-762000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-798000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-490000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-832000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-682000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-960000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-791000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-665000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-549000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-829000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-659000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-725000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-650000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5079000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>647000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>573000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>97000</v>
       </c>
       <c r="AD94" s="3">
         <v>97000</v>
       </c>
       <c r="AE94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8796,8 +9028,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8822,86 +9055,89 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>566000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AE96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AF96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9004,8 +9240,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9108,8 +9347,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9212,316 +9454,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5571000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-634000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5945000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-156000</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>53000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-235000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-185000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-56000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>53000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-235000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-185000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-56000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-129000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-127000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>36000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-81000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>115000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>31000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>40000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-170000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>56000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-65000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>18000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>82000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>47000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>82000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>159000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>128000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1927000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2676000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2654000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1488000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>650000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>742000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>144000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-504000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1174000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>82000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>281000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>788000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9114000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5065000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1501000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,455 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19776000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21882000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21737000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20532000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20195000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21441000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21871000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20553000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20068000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20773000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20612000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19515000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19381000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20953000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20338000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18946000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18109000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>19745000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19318000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>17698000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17214000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>18240000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17798000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17094000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9671000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10390000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10380000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10254000</v>
       </c>
-      <c r="G9" s="3">
-        <v>9811000</v>
-      </c>
       <c r="H9" s="3">
+        <v>9855000</v>
+      </c>
+      <c r="I9" s="3">
         <v>10144000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10501000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10453000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10404000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10897000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10846000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10802000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10326000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10664000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10365000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9791000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8922000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9253000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9142000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8659000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8518000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8806000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8653000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8410000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10105000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11492000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11357000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10278000</v>
       </c>
-      <c r="G10" s="3">
-        <v>10384000</v>
-      </c>
       <c r="H10" s="3">
+        <v>10340000</v>
+      </c>
+      <c r="I10" s="3">
         <v>11297000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11370000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10100000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9664000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9876000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9766000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8713000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9055000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10289000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9973000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9155000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9187000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10492000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10176000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9039000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8696000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>9434000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9145000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8684000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>125000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>273000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1142,8 +1154,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,11 +1166,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1165,11 +1178,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1249,8 +1262,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1356,34 +1372,37 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E14" s="3">
         <v>48000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>886000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>413000</v>
       </c>
-      <c r="G14" s="3">
-        <v>70000</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>1341000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>338000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1394,20 +1413,20 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1415,86 +1434,89 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>362000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>222000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>105000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>93000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8985000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>116000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>177000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>554000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>205000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>154000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>157000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>249000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>157000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>175000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E15" s="3">
         <v>706000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>728000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>761000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>712000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>721000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>702000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>706000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>692000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1592,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,222 +1631,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15169000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15934000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15702000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16139000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>15735000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15562000</v>
       </c>
-      <c r="H17" s="3">
-        <v>15562000</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16006000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15731000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15734000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15988000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15673000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15917000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15357000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15785000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15315000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15406000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14324000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14365000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14037000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14221000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>13764000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13763000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13509000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22287000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4607000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5948000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6035000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4393000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4633000</v>
-      </c>
       <c r="H18" s="3">
+        <v>4460000</v>
+      </c>
+      <c r="I18" s="3">
         <v>5879000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5865000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4822000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4334000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4785000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4939000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3598000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4024000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5168000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5023000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3540000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3785000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5380000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5281000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3477000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3450000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4477000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4289000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1859,543 +1891,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-214000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-67000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-93000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-159000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-262000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-73000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>127000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-93000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>221000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>181000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>167000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>156000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>177000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>121000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>141000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>198000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-360000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>152000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>141000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>148000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>155000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>162000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>239000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>182000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>167000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>161000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>90000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>358000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>218000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>94000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>72000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5511000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6721000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6856000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5157000</v>
       </c>
-      <c r="G21" s="3">
-        <v>5504000</v>
-      </c>
       <c r="H21" s="3">
+        <v>5434000</v>
+      </c>
+      <c r="I21" s="3">
         <v>6673000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6601000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5401000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5119000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5659000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5783000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4487000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4870000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6029000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5855000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4391000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4666000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5691000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6104000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4432000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4397000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5309000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5174000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E22" s="3">
         <v>240000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>238000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>220000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>233000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>248000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>225000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>240000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>222000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>171000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>123000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>115000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>109000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>106000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>109000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>117000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>106000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>143000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>136000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>157000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>100000</v>
       </c>
       <c r="X22" s="3">
         <v>100000</v>
       </c>
       <c r="Y22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="Z22" s="3">
         <v>108000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>111000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>131000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>138000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>129000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>272000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>133000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>244000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>115000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>116000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>122000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4660000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5846000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5139000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3870000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4593000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4496000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5802000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4233000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4288000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4835000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4997000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3650000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4071000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5239000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5035000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3564000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3877000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4877000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5297000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3461000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3498000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4532000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4343000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1187000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1152000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>726000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>812000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1003000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1246000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>841000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>864000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>876000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1034000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>592000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>704000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>997000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>909000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>656000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>628000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>990000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>989000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>675000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>541000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>789000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>726000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>172000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>502000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>729000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>499000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>613000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>872000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>881000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>725000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>780000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>695000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2501,222 +2549,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3792000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4659000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3987000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3144000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3781000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3493000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4556000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3392000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3424000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3959000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3963000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3058000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3367000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4242000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4126000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2908000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3249000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3887000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4308000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2786000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2957000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3743000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3617000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3698000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4558000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3887000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3062000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3685000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3398000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4451000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3312000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3328000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3863000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3868000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2979000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3287000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4153000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4042000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2832000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3204000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3788000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4211000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2730000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2853000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3653000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3528000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2822,8 +2879,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2887,17 +2947,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2905,18 +2965,18 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>100000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
@@ -2924,13 +2984,16 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3099,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3143,222 +3209,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E32" s="3">
         <v>67000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>93000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
-        <v>159000</v>
-      </c>
       <c r="H32" s="3">
+        <v>262000</v>
+      </c>
+      <c r="I32" s="3">
         <v>73000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-127000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>93000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-221000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-181000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-167000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-156000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-177000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-121000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-141000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-198000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>360000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-152000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-141000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-148000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-155000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-162000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-239000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>26000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>497000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3769000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4630000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3959000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3137000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3754000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3468000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4521000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3384000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3397000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3863000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3868000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2979000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3287000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4153000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4042000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2832000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3204000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3788000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4211000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2730000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2853000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3653000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3528000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3464,227 +3539,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3769000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4630000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3959000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3137000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3754000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3468000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4521000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3384000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3397000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3863000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3868000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2979000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3287000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4153000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4042000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2832000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3204000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3788000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4211000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2730000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2853000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3653000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3528000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3722,8 +3806,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3761,115 +3846,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9116000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10230000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12156000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9482000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6828000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7890000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9733000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8246000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7596000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6854000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6710000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7214000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8526000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11544000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10370000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10288000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10007000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11941000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13392000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16181000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>15393000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6279000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9304000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3940,257 +4029,266 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>6048000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6139000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6234000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6314000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6118000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6124000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6334000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="J43" s="3">
-        <v>5471000</v>
       </c>
       <c r="K43" s="3">
         <v>5471000</v>
       </c>
       <c r="L43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="M43" s="3">
         <v>5767000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5720000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5143000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5513000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5241000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5662000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4725000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4861000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4819000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5043000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4178000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4640000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5196000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5143000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4951000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7400000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7020000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7287000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7016000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7078000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7152000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7117000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7073000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7483000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7541000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7590000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6924000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7101000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6673000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6307000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5983000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6002000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5957000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5707000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5498000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5330000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5521000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5465000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5017000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4218,193 +4316,199 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>1704000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2501000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2372000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2276000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2087000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1997000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2095000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1738000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1938000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1884000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2130000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1777000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1921000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2013000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2218000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>24435000</v>
+      </c>
+      <c r="E46" s="3">
         <v>25642000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27449000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24709000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22458000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23111000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24940000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22648000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22305000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21866000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22521000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21653000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>23416000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>25545000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24336000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23091000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>22608000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24655000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>26026000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>27987000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27140000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18917000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>21925000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22473000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4429,23 +4533,23 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>91000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>60000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>66000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>113000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>126000</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>8</v>
@@ -4459,8 +4563,8 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4510,222 +4614,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22728000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22074000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22506000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23027000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22027000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22132000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21636000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22690000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21564000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21167000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20593000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21195000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21323000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21357000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21392000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21686000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21103000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21416000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20876000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21542000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21314000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>22153000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21788000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21271000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62312000</v>
+      </c>
+      <c r="E49" s="3">
         <v>61731000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63023000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>62350000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>62760000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>63218000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63876000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>64442000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>64550000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63545000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>62226000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>63379000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64623000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>63853000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>63997000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>64566000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>64270000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>65245000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>64383000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>63693000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>63451000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>63978000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>63607000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>64488000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4831,8 +4944,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4938,115 +5054,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13509000</v>
+      </c>
+      <c r="E52" s="3">
         <v>13192000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13504000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12284000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12353000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12248000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12079000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11049000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11341000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11077000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10876000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10868000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10729000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10661000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9944000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9964000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8797000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8796000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8614000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7478000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6655000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6675000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6738000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6863000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5152,115 +5274,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>122984000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122639000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>126482000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122370000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>119598000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>120709000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122531000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>120829000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119851000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>117715000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116282000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>117208000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>120217000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>121416000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>119669000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119307000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>116778000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>120112000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119899000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>120700000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>118560000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>111723000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>114058000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>115095000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5298,8 +5426,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5337,222 +5466,229 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14512000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14495000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15350000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15364000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13691000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14234000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14435000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14598000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13790000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14153000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14845000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14882000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14175000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14154000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14223000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13720000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12134000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12027000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11935000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12071000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10464000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10781000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10951000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11260000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9889000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9424000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10409000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7465000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7729000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10616000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11811000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11082000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13717000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14300000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11717000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8645000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>9902000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>13331000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11989000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8889000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8773000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8586000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>7707000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11183000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>12701000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9153000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>9352000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>9697000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5562,11 +5698,11 @@
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
@@ -5574,413 +5710,425 @@
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>3917000</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10293000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10056000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9554000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10324000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10542000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10377000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10523000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11109000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11131000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10366000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9722000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9731000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10230000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9950000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9054000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34248000</v>
+      </c>
+      <c r="E60" s="3">
         <v>33797000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36420000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33627000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32340000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35950000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37158000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35756000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38030000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38746000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36618000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33081000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34401000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38027000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36589000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33132000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>32016000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31744000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30008000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32976000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32896000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30164000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30253000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30011000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24252000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25263000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25744000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>26260000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24253000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23096000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>24069000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25418000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>22874000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20582000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>21286000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22848000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>23767000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>22322000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20558000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23099000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>21053000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>22514000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23948000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23537000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23310000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>18985000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>20161000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20395000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5458000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5411000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5758000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1872000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6388000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6616000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6477000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2306000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7104000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13662000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14044000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14425000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16303000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16174000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16114000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16422000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16790000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>17314000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17367000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17309000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16413000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16666000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16660000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17110000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6086,8 +6234,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6193,8 +6344,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6300,115 +6454,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70439000</v>
+      </c>
+      <c r="E66" s="3">
         <v>71196000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74342000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71812000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>69265000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>71881000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74518000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>73764000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>74430000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>73260000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72207000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>70619000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74739000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>76798000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>73558000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>72929000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70182000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>71931000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>71717000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>74179000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73020000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>66185000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>67480000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>67901000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6446,8 +6606,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6553,8 +6714,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6660,115 +6824,121 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E70" s="3">
         <v>788000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>791000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>798000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>801000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>809000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>812000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>819000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>822000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>831000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>834000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>843000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>846000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>856000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>859000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>870000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>873000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>885000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>888000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>897000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>900000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>911000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>915000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>928000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>933000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>946000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>951000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>967000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>972000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>986000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>991000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6874,115 +7044,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>128919000</v>
+      </c>
+      <c r="E72" s="3">
         <v>127544000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>125361000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>123811000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>123132000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>121617000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>120443000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>118170000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>117082000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>115858000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>114163000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>112429000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>111645000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>110393000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>108361000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>106374000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>105674000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>104361000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>102539000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>100239000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>99474000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>98414000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>96625000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>94918000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7088,8 +7264,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7195,8 +7374,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7302,115 +7484,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51491000</v>
+      </c>
+      <c r="E76" s="3">
         <v>50380000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51049000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>49488000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49257000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>47725000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46880000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>45958000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>44318000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>43624000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43241000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45746000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44632000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43762000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45252000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45508000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45723000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>47296000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>47294000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45624000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>44640000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>44627000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>45663000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>46266000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7516,227 +7704,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3769000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4630000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3959000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3137000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3754000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3468000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4521000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3384000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3397000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3863000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3868000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2979000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3287000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4153000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4042000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2832000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3204000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3788000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4211000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2730000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2853000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3653000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3528000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7774,115 +7971,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>628000</v>
+      </c>
+      <c r="E83" s="3">
         <v>637000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>615000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>620000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>610000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>574000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>583000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>640000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>611000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>653000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>663000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>722000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>690000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>684000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>711000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>710000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>683000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>671000</v>
       </c>
       <c r="U83" s="3">
         <v>671000</v>
       </c>
       <c r="V83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="W83" s="3">
         <v>814000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>799000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>677000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>723000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>820000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>711000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>650000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>643000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>750000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>716000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>676000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>692000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>720000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>707000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7988,8 +8189,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8095,8 +8299,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8202,8 +8409,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8309,8 +8519,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8416,115 +8629,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3705000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4825000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4302000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5754000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4088000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5100000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4904000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5341000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3863000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3574000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4070000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3713000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3246000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5121000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4643000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4121000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4087000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5424000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4739000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4806000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4064000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4364000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4169000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4151000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8562,115 +8781,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-859000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-925000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-993000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-783000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-797000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-817000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-925000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-734000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-730000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-708000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-890000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-692000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-747000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-626000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-714000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-656000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-567000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-850000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-658000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-731000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-605000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-814000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8776,8 +8999,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8883,115 +9109,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-726000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-921000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-518000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-762000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-798000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-490000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-832000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-682000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-960000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-791000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-665000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-549000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-829000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-659000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-725000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-650000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>5079000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>647000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>573000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>97000</v>
       </c>
       <c r="AE94" s="3">
         <v>97000</v>
       </c>
       <c r="AF94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>100000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9029,8 +9261,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9058,86 +9291,89 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>566000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AF96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AG96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9243,8 +9479,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9350,8 +9589,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9457,325 +9699,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4215000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5571000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-634000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5945000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-119000</v>
+      </c>
+      <c r="E101" s="3">
         <v>107000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-156000</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>12000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>53000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-235000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-185000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-56000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>53000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-235000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-185000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-56000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-129000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-127000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>36000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-81000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>115000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>31000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>40000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-170000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>56000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-65000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>18000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>82000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>47000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>82000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>159000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1114000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1927000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2676000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2654000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1488000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>650000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>742000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>144000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-504000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1174000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>82000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>281000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>788000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9114000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5065000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1501000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="38" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="39" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>20889000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19776000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21882000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21737000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20532000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20195000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21441000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21871000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20553000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20068000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20773000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20612000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19515000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19381000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20953000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>20338000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18946000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>18109000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>19745000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>19318000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>17698000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>17214000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>18240000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17798000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17094000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10572000</v>
+      </c>
+      <c r="E9" s="3">
         <v>9671000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10390000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10380000</v>
       </c>
-      <c r="G9" s="3">
-        <v>10254000</v>
-      </c>
       <c r="H9" s="3">
+        <v>10100000</v>
+      </c>
+      <c r="I9" s="3">
         <v>9855000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10144000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10501000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10453000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10404000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10897000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10846000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10802000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10326000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10664000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10365000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9791000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8922000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9253000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9142000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8659000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>8518000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8806000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8653000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8410000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10317000</v>
+      </c>
+      <c r="E10" s="3">
         <v>10105000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11492000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>11357000</v>
       </c>
-      <c r="G10" s="3">
-        <v>10278000</v>
-      </c>
       <c r="H10" s="3">
+        <v>10432000</v>
+      </c>
+      <c r="I10" s="3">
         <v>10340000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11297000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11370000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10100000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9664000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9876000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9766000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8713000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9055000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10289000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9973000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9155000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9187000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10492000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10176000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9039000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8696000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9434000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9145000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8684000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>125000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>273000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,13 +1167,14 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>2100000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1169,11 +1182,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1181,11 +1194,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1265,8 +1278,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1375,37 +1391,40 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E14" s="3">
         <v>55000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>48000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>886000</v>
       </c>
-      <c r="G14" s="3">
-        <v>413000</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="3">
+        <v>665000</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1341000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>338000</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1416,20 +1435,20 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1437,89 +1456,92 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>362000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>222000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>105000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>93000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8985000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>116000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>177000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>554000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>205000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>154000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>157000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>249000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>157000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>175000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>723000</v>
+      </c>
+      <c r="E15" s="3">
         <v>690000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>706000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>728000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>761000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>712000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>721000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>702000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>706000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>692000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,228 +1657,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15636000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15169000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15934000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15702000</v>
       </c>
-      <c r="G17" s="3">
-        <v>16139000</v>
-      </c>
       <c r="H17" s="3">
+        <v>15585000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15735000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15562000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16006000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15731000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15734000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15988000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15673000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15917000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15357000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15785000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15315000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15406000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14324000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14365000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14037000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14221000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>13764000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>13763000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13509000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22287000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5253000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4607000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5948000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6035000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4393000</v>
-      </c>
       <c r="H18" s="3">
+        <v>4947000</v>
+      </c>
+      <c r="I18" s="3">
         <v>4460000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5879000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5865000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4822000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4334000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4785000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4939000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3598000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4024000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5168000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5023000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3540000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3785000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5380000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5281000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3477000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3450000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4477000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4289000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1892,558 +1924,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-214000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-67000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-93000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H20" s="3">
+        <v>299000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-262000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-73000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>127000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-93000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>221000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>181000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>167000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>156000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>177000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>121000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>141000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>198000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-360000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>152000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>141000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>148000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>155000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>162000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>239000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>182000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>167000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>161000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>90000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>358000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>218000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>94000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>72000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5484000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5511000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6721000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6856000</v>
       </c>
-      <c r="G21" s="3">
-        <v>5157000</v>
-      </c>
       <c r="H21" s="3">
+        <v>5409000</v>
+      </c>
+      <c r="I21" s="3">
         <v>5434000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6673000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6601000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5401000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5119000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5659000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5783000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4487000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4870000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6029000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5855000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4391000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4666000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5691000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6104000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4432000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4397000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5309000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5174000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E22" s="3">
         <v>217000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>240000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>238000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>220000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>233000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>248000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>225000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>240000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>222000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>171000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>123000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>115000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>109000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>106000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>109000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>117000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>106000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>143000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>136000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>157000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100000</v>
       </c>
       <c r="Y22" s="3">
         <v>100000</v>
       </c>
       <c r="Z22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AA22" s="3">
         <v>108000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>111000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>131000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>138000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>129000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>272000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>133000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>244000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>115000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>116000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>96000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>122000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4521000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4660000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5846000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5139000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3870000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4593000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4496000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5802000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4233000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4288000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4835000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4997000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3650000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4071000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5239000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5035000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3564000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3877000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4877000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5297000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3461000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3498000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4532000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4343000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>895000</v>
+      </c>
+      <c r="E24" s="3">
         <v>868000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1187000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1152000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>726000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>812000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1003000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1246000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>841000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>864000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>876000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1034000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>592000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>704000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>997000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>909000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>656000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>628000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>990000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>989000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>675000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>541000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>789000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>726000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>172000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>502000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>729000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>499000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>613000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>872000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>881000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>725000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>780000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>695000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,228 +2600,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3626000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3792000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4659000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3987000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3144000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3781000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3493000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4556000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3392000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3424000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3959000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3963000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3058000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3367000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4242000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4126000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2908000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3249000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3887000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4308000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2786000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2957000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3743000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3617000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3539000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3698000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4558000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3887000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3062000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3685000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3398000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4451000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3312000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3328000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3863000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3868000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2979000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3287000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4153000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4042000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2832000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3204000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3788000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4211000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2730000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2853000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3653000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3528000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2882,8 +2939,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2950,17 +3010,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2968,18 +3028,18 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>100000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
@@ -2987,13 +3047,16 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3102,8 +3165,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3212,228 +3278,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-492000</v>
+      </c>
+      <c r="E32" s="3">
         <v>214000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>67000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>93000</v>
       </c>
-      <c r="G32" s="3">
-        <v>3000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-299000</v>
+      </c>
+      <c r="I32" s="3">
         <v>262000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>73000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-127000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>93000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-221000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-181000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-167000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-156000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-177000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-121000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-141000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-198000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>360000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-152000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-141000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-148000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-155000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-239000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>26000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>497000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3769000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4630000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3959000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3137000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3754000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3468000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4521000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3384000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3397000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3863000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3868000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2979000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3287000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4153000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4042000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2832000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3204000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3788000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4211000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2730000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2853000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3653000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3528000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3542,233 +3617,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3769000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4630000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3959000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3137000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3754000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3468000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4521000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3384000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3397000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3863000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3868000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2979000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3287000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4153000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4042000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2832000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3204000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3788000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4211000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2730000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2853000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3653000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3528000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3807,8 +3891,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3847,118 +3932,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9556000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9116000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10230000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12156000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9482000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6828000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7890000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9733000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8246000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7596000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6854000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6710000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7214000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8526000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11544000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10370000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10288000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10007000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11941000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13392000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16181000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>15393000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6279000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9304000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4032,268 +4121,277 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>6048000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6185000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6139000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6234000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6314000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6118000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6124000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6334000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="K43" s="3">
-        <v>5471000</v>
       </c>
       <c r="L43" s="3">
         <v>5471000</v>
       </c>
       <c r="M43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="N43" s="3">
         <v>5767000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5720000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5143000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5513000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5241000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5662000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4725000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4861000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4819000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5043000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4178000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4640000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5196000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>5143000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4951000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7550000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7400000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7020000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7287000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7016000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7078000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7152000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7117000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7073000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7483000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7541000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7590000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6924000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7101000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6673000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6307000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5983000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6002000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5957000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5707000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5498000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5330000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5521000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5465000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5017000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>1000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4319,196 +4417,202 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>1704000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2501000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2372000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2276000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2087000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1997000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2095000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1738000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1938000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1884000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2130000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1777000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1921000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2013000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2218000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25392000</v>
+      </c>
+      <c r="E46" s="3">
         <v>24435000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25642000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27449000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24709000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22458000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>23111000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24940000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22648000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>22305000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21866000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22521000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21653000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>23416000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25545000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>24336000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23091000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>22608000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24655000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>26026000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>27987000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>27140000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18917000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>21925000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>22473000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4536,23 +4640,23 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>91000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>60000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>66000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>113000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>126000</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
@@ -4566,8 +4670,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4617,228 +4721,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24822000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22728000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22074000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22506000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23027000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22027000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22132000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21636000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22690000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21564000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21167000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20593000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21195000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21323000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21357000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21392000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21686000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21103000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21416000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>20876000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21542000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21314000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22153000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21788000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21271000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>63560000</v>
+      </c>
+      <c r="E49" s="3">
         <v>62312000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>61731000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63023000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>62350000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>62760000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63218000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>63876000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>64442000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>64550000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63545000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>62226000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>63379000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>64623000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>63853000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>63997000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>64566000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>64270000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>65245000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>64383000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>63693000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>63451000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>63978000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>63607000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>64488000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4947,8 +5060,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5057,118 +5173,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11457000</v>
+      </c>
+      <c r="E52" s="3">
         <v>13509000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13192000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13504000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12284000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12353000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12248000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12079000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11049000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11341000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11077000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10876000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10868000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10729000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10661000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9944000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9964000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8797000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8796000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8614000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7478000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6655000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6675000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6738000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6863000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5277,118 +5399,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>125231000</v>
+      </c>
+      <c r="E54" s="3">
         <v>122984000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>122639000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>126482000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122370000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119598000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>120709000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>122531000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120829000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119851000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117715000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>116282000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117208000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>120217000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>121416000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>119669000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>119307000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>116778000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>120112000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>119899000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120700000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>118560000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>111723000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>114058000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>115095000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5427,8 +5555,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5467,233 +5596,240 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15227000</v>
+      </c>
+      <c r="E57" s="3">
         <v>14512000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14495000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15350000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15364000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13691000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14234000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14435000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14598000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13790000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14153000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14845000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14882000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14175000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14154000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14223000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13720000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12134000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12027000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11935000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12071000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10464000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10781000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10951000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>11260000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10395000</v>
+      </c>
+      <c r="E58" s="3">
         <v>9889000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9424000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10409000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7465000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7729000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10616000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11811000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11082000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13717000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14300000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11717000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8645000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9902000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>13331000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11989000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>8889000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8773000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8586000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7707000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11183000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>12701000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>9153000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>9352000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9697000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>4286000</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
@@ -5701,11 +5837,11 @@
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -5713,422 +5849,434 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>3917000</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10293000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10056000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9554000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10324000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10542000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10377000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10523000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11109000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11131000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10366000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9722000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9731000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10230000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9950000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9054000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36058000</v>
+      </c>
+      <c r="E60" s="3">
         <v>34248000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33797000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36420000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33627000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32340000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35950000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37158000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35756000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38030000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38746000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>36618000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33081000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>34401000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38027000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36589000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33132000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>32016000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31744000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>30008000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32976000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>32896000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30164000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>30253000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30011000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>26131000</v>
+      </c>
+      <c r="E61" s="3">
         <v>24252000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>25263000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25744000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>26260000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>24253000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23096000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24069000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25418000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22874000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20582000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>21286000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22848000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>23767000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22322000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>20558000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23099000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>21053000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>22514000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23948000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>23537000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>23310000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>18985000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>20161000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>20395000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1267000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5458000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5411000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5758000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1872000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6388000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6616000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6477000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2306000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7104000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13662000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14044000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>14425000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16303000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16174000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16114000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16422000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16790000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17314000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17367000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17309000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16413000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16666000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16660000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>17110000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6237,8 +6385,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6347,8 +6498,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6457,118 +6611,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>72947000</v>
+      </c>
+      <c r="E66" s="3">
         <v>70439000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71196000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74342000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71812000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>69265000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71881000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>74518000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73764000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74430000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73260000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72207000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70619000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74739000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>76798000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>73558000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>72929000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70182000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>71931000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>71717000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>74179000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>73020000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>66185000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>67480000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>67901000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6607,8 +6767,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6717,8 +6878,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6827,118 +6991,124 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>777000</v>
+      </c>
+      <c r="E70" s="3">
         <v>781000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>788000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>791000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>798000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>801000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>809000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>812000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>819000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>822000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>831000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>834000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>843000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>846000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>856000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>859000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>870000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>873000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>885000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>888000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>897000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>900000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>911000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>915000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>928000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>933000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>946000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>951000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>967000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>972000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>986000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>991000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7047,118 +7217,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>129973000</v>
+      </c>
+      <c r="E72" s="3">
         <v>128919000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>127544000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>125361000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>123811000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>123132000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>121617000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>120443000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>118170000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>117082000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>115858000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>114163000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>112429000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>111645000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>110393000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>108361000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>106374000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>105674000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>104361000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>102539000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>100239000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>99474000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>98414000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>96625000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>94918000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7267,8 +7443,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7377,8 +7556,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7487,118 +7669,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51235000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51491000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>50380000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51049000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>49488000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>49257000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>47725000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46880000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>45958000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44318000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>43624000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43241000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>45746000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>44632000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43762000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45252000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45508000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45723000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>47296000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>47294000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45624000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>44640000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>44627000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>45663000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46266000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7707,233 +7895,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3615000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3769000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4630000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3959000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3137000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3754000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3468000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4521000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3384000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3397000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3863000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3868000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2979000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3287000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4153000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4042000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2832000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3204000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3788000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4211000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2730000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2853000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3653000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3528000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7972,118 +8169,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>678000</v>
+      </c>
+      <c r="E83" s="3">
         <v>628000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>637000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>615000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>620000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>610000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>574000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>583000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>640000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>611000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>653000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>663000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>722000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>690000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>684000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>711000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>710000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>683000</v>
-      </c>
-      <c r="U83" s="3">
-        <v>671000</v>
       </c>
       <c r="V83" s="3">
         <v>671000</v>
       </c>
       <c r="W83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="X83" s="3">
         <v>814000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>799000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>677000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>723000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>820000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>711000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>650000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>643000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>750000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>716000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>676000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>692000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>720000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>665000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>707000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8192,8 +8393,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8302,8 +8506,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8412,8 +8619,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8522,8 +8732,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8632,118 +8845,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4985000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3705000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4825000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4302000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5754000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4088000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5100000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4904000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5341000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3863000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3574000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4070000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3713000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3246000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5121000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4643000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4121000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4087000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5424000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4739000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4806000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4064000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4364000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4169000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4151000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8782,118 +9001,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-996000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-859000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-925000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-993000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-783000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-797000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-817000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-925000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-734000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-730000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-708000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-890000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-692000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-747000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-626000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-714000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-656000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-567000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-850000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-658000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-731000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-605000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-814000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9002,8 +9225,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9112,118 +9338,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1063000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-726000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-921000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-518000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-762000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-798000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-490000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-832000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-682000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-960000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-791000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-665000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-549000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-829000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-659000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-725000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-650000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>5079000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>647000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>573000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>97000</v>
       </c>
       <c r="AF94" s="3">
         <v>97000</v>
       </c>
       <c r="AG94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>100000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9262,8 +9494,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9294,86 +9527,89 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>566000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AG96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AH96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9482,8 +9718,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9592,8 +9831,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9702,334 +9944,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3616000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4215000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5571000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-634000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5945000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-119000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>107000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-156000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-235000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-185000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-56000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>53000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-235000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-185000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-129000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-127000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>36000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-81000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>115000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>31000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>40000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-170000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>56000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>7000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>18000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>82000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>47000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>82000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>159000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>128000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1114000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1927000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2676000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2654000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1488000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>650000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>742000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>144000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-504000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1174000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>82000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>281000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>788000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9114000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5065000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1501000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,491 +656,503 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="40" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22208000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22386000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20889000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19776000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21882000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21737000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20532000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20195000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21441000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21871000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20553000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20068000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20773000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20612000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19515000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19381000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20953000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20338000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18946000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18109000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>19745000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19318000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>17698000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17214000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>18240000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>17798000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17094000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10654000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10787000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10572000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9671000</v>
       </c>
-      <c r="G9" s="3">
-        <v>10390000</v>
-      </c>
       <c r="H9" s="3">
+        <v>10418000</v>
+      </c>
+      <c r="I9" s="3">
         <v>10421000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10100000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9855000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10144000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10501000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10453000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10404000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10897000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10846000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10802000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10326000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10664000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10365000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9791000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8922000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9253000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9142000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>8659000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8518000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8806000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8653000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8410000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>11554000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11599000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10317000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10105000</v>
       </c>
-      <c r="G10" s="3">
-        <v>11492000</v>
-      </c>
       <c r="H10" s="3">
+        <v>11464000</v>
+      </c>
+      <c r="I10" s="3">
         <v>11316000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10432000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10340000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11297000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11370000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10100000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9664000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9876000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9766000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8713000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9055000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>10289000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>9973000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9155000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9187000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10492000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10176000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>9039000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8696000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>9434000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9145000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8684000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>273000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,19 +1193,20 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>2100000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1201,11 +1214,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1213,11 +1226,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1297,8 +1310,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1413,43 +1429,46 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>369000</v>
+      </c>
+      <c r="E14" s="3">
         <v>215000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>132000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>55000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>48000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>665000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1341000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>338000</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1460,20 +1479,20 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1481,95 +1500,98 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>362000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>222000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>105000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>93000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8985000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>116000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>177000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>554000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>205000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>154000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>157000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>249000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>157000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>175000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>802000</v>
+      </c>
+      <c r="E15" s="3">
         <v>761000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>723000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>690000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>706000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>728000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>761000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>712000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>721000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>702000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>706000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>692000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1667,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,240 +1709,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16368000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16212000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15636000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15169000</v>
       </c>
-      <c r="G17" s="3">
-        <v>15934000</v>
-      </c>
       <c r="H17" s="3">
+        <v>15987000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15797000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15585000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15735000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15562000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16006000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15731000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15734000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15988000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15673000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15917000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15357000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15785000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15315000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15406000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>14324000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14365000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14037000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14221000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>13764000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13763000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13509000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22287000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5840000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6174000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5253000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4607000</v>
       </c>
-      <c r="G18" s="3">
-        <v>5948000</v>
-      </c>
       <c r="H18" s="3">
+        <v>5895000</v>
+      </c>
+      <c r="I18" s="3">
         <v>5940000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4947000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4460000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5879000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5865000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4822000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4334000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4785000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4939000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3598000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4024000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5168000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5023000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3540000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3785000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5380000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5281000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3477000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3450000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4477000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4289000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1958,588 +1990,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-164000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>492000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-214000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-67000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-72000</v>
+      </c>
+      <c r="I20" s="3">
         <v>698000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>299000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-262000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-73000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>127000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-93000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>221000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>181000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>167000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>156000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>177000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>121000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>141000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>198000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-360000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>152000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>141000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>148000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>155000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>162000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>239000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>182000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>167000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>161000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>90000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>358000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>218000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>94000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>72000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6697000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7099000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5484000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5511000</v>
       </c>
-      <c r="G21" s="3">
-        <v>6721000</v>
-      </c>
       <c r="H21" s="3">
+        <v>6673000</v>
+      </c>
+      <c r="I21" s="3">
         <v>5970000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5409000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5434000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6673000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6601000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5401000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5119000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5659000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5783000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4487000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4870000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6029000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5855000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4391000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4666000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5691000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6104000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4432000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4397000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5309000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5174000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E22" s="3">
         <v>197000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>212000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>217000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>240000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>238000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>220000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>233000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>248000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>225000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>240000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>222000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>171000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>123000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>115000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>109000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>106000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>109000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>117000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>106000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>143000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>136000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>157000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>100000</v>
       </c>
       <c r="AA22" s="3">
         <v>100000</v>
       </c>
       <c r="AB22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AC22" s="3">
         <v>108000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>111000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>131000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>138000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>129000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>272000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>133000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>244000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>115000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>116000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>96000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>122000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5421000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6034000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4521000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4660000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5846000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5139000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3870000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4593000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4496000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5802000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4233000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4288000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4835000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4997000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3650000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4071000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5239000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5035000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3564000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3877000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4877000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5297000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3461000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3498000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4532000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4343000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1090000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1253000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>895000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>868000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1187000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1152000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>726000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>812000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1003000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1246000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>841000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>864000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>876000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1034000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>592000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>704000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>997000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>909000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>656000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>628000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>990000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>989000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>675000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>541000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>789000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>726000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>172000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>502000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>729000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>499000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>613000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>872000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>881000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>725000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>780000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>695000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2654,240 +2702,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4331000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4781000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3626000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3792000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4659000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3987000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3144000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3781000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3493000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4556000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3392000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3424000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3959000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3963000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3058000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3367000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4242000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4126000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2908000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3249000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3887000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4308000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2786000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2957000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3743000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3617000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4246000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4677000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3539000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3698000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4558000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3887000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3062000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3685000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3398000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4451000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3312000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3328000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3863000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3868000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2979000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3287000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4153000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4042000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2832000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3204000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3788000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4211000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2730000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2853000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3653000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3528000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3002,8 +3059,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3076,17 +3136,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3094,18 +3154,18 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>100000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
         <v>0</v>
       </c>
@@ -3113,13 +3173,16 @@
         <v>0</v>
       </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3234,8 +3297,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3350,240 +3416,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>55000</v>
+      </c>
+      <c r="E32" s="3">
         <v>164000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-492000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>214000</v>
       </c>
-      <c r="G32" s="3">
-        <v>67000</v>
-      </c>
       <c r="H32" s="3">
+        <v>72000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-698000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-299000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>262000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>73000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-127000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>93000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-221000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-181000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-167000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-156000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-177000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-121000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-141000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-198000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>360000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-152000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-141000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-148000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-239000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>26000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>497000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4319000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4750000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3615000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3769000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4630000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3959000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3137000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3754000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3468000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4521000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3384000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3397000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3863000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3868000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2979000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3287000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4153000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4042000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2832000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3204000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3788000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4211000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2730000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2853000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3653000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3528000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3698,245 +3773,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4319000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4750000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3615000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3769000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4630000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3959000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3137000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3754000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3468000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4521000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3384000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3397000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3863000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3868000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2979000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3287000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4153000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4042000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2832000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3204000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3788000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4211000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2730000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2853000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3653000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3528000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3977,8 +4061,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4019,124 +4104,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10825000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11171000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9556000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9116000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10230000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12156000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9482000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6828000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7890000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9733000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8246000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7596000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6854000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6710000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7214000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8526000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11544000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10370000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10288000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10007000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11941000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13392000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16181000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15393000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6279000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9304000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4216,286 +4305,295 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>6048000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6279000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6487000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6185000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6139000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6234000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6314000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6118000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6124000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6334000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>5471000</v>
       </c>
       <c r="N43" s="3">
         <v>5471000</v>
       </c>
       <c r="O43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="P43" s="3">
         <v>5767000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5720000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5143000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5513000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5241000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5662000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4725000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4861000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4819000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5043000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4178000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4640000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5196000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5143000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4951000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7818000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7848000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7550000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7400000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7020000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7287000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7016000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7078000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7152000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7117000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7073000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7483000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7541000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7590000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6924000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7101000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6673000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6307000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5983000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6002000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5957000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5707000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5498000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5330000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5521000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5465000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5017000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -4521,202 +4619,208 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>1704000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2501000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2372000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2276000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2087000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1997000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2095000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1738000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1938000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1884000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2130000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1777000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1921000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2013000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2218000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>26588000</v>
+      </c>
+      <c r="E46" s="3">
         <v>27118000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>25392000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>24435000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>25642000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27449000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24709000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22458000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23111000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24940000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22648000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22305000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21866000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22521000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21653000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>23416000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25545000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24336000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23091000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22608000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>24655000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>26026000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27987000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27140000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18917000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>21925000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>22473000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4750,23 +4854,23 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
         <v>91000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>60000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>66000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>113000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>126000</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>8</v>
@@ -4780,8 +4884,8 @@
       <c r="W47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4831,240 +4935,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24487000</v>
+      </c>
+      <c r="E48" s="3">
         <v>24119000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24822000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22728000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22074000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22506000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23027000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22027000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22132000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21636000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22690000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21564000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21167000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20593000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21195000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21323000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21357000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21392000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21686000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21103000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21416000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20876000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>21542000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21314000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22153000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21788000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21271000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>63402000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63461000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63560000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>62312000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>61731000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>63023000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>62350000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>62760000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>63218000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63876000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>64442000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64550000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>63545000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>62226000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>63379000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>64623000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>63853000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63997000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>64566000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>64270000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>65245000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>64383000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>63693000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>63451000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>63978000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>63607000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>64488000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5179,8 +5292,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5295,124 +5411,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12809000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12901000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11457000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13509000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13192000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13504000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12284000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12353000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12248000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12079000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11049000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11341000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11077000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10876000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10868000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10729000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10661000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9944000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9964000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8797000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8796000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8614000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>7478000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6655000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6675000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6738000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6863000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5527,124 +5649,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>127286000</v>
+      </c>
+      <c r="E54" s="3">
         <v>127599000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>125231000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>122984000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122639000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>126482000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>122370000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119598000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>120709000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122531000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120829000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119851000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117715000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>116282000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>117208000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>120217000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>121416000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>119669000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119307000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>116778000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>120112000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>119899000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>120700000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>118560000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>111723000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>114058000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>115095000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5685,8 +5813,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5727,251 +5856,258 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15173000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15609000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15227000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14512000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14495000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15350000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15364000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13691000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14234000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14435000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14598000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13790000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14153000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14845000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14882000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14175000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14154000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14223000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13720000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12134000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12027000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11935000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>12071000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10464000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10781000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10951000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11260000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11062000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11631000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>10395000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9889000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9424000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10409000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7465000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7729000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10616000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11811000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11082000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>13717000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14300000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11717000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>8645000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9902000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>13331000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11989000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>8889000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8773000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8586000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7707000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11183000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12701000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9153000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>9352000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9697000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4286000</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -5979,11 +6115,11 @@
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -5991,440 +6127,452 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>3917000</v>
       </c>
-      <c r="N59" s="3" t="s">
+      <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10293000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10056000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9554000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>10324000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10542000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10377000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10523000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11109000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11131000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10366000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9722000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9731000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10230000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9950000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9054000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36699000</v>
+      </c>
+      <c r="E60" s="3">
         <v>37995000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36058000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34248000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33797000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36420000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33627000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32340000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35950000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>37158000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>35756000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38030000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38746000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36618000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33081000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>34401000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38027000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>36589000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>33132000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>32016000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>31744000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30008000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>32976000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32896000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30164000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30253000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30011000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>25577000</v>
+      </c>
+      <c r="E61" s="3">
         <v>24315000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>26131000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>24252000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25263000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25744000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26260000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>24253000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23096000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>24069000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>25418000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>22874000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20582000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>21286000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22848000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>23767000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22322000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>20558000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>23099000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>21053000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>22514000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>23948000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23537000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23310000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>18985000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>20161000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20395000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5719000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5845000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1267000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5458000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5411000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5758000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1872000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6388000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6616000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6477000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2306000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7104000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13662000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>14044000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14425000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>16303000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16174000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16114000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16422000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16790000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>17314000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17367000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17309000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>16413000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16666000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16660000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>17110000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6539,8 +6687,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6655,8 +6806,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6771,124 +6925,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>73969000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74048000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>72947000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>70439000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71196000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74342000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>71812000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>69265000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71881000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74518000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73764000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74430000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73260000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72207000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70619000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>74739000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>76798000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>73558000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>72929000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70182000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>71931000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>71717000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>74179000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>73020000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>66185000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>67480000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>67901000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6929,8 +7089,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7045,8 +7206,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7161,124 +7325,130 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>767000</v>
+      </c>
+      <c r="E70" s="3">
         <v>770000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>777000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>781000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>788000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>791000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>798000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>801000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>809000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>812000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>819000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>822000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>831000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>834000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>843000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>846000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>856000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>859000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>870000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>873000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>885000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>888000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>897000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>900000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>911000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>915000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>928000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>933000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>946000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>951000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>967000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>972000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>986000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>991000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7393,124 +7563,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>133981000</v>
+      </c>
+      <c r="E72" s="3">
         <v>132212000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>129973000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>128919000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>127544000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>125361000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>123811000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>123132000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>121617000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>120443000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>118170000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>117082000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>115858000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>114163000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>112429000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>111645000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>110393000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>108361000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>106374000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>105674000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>104361000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>102539000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>100239000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>99474000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>98414000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>96625000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>94918000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7625,8 +7801,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7741,8 +7920,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7857,124 +8039,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>52274000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52500000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51235000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51491000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>50380000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51049000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49488000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49257000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47725000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>46880000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>45958000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44318000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43624000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43241000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45746000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44632000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>43762000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45252000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45508000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45723000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>47296000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47294000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>45624000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>44640000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>44627000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>45663000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46266000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8089,245 +8277,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4319000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4750000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3615000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3769000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4630000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3959000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3137000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3754000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3468000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4521000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3384000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3397000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3863000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3868000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2979000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3287000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4153000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4042000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2832000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3204000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3788000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4211000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2730000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2853000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3653000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3528000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8368,124 +8565,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>626000</v>
+      </c>
+      <c r="E83" s="3">
         <v>645000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>678000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>628000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>637000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>615000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>620000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>610000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>574000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>583000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>640000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>611000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>653000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>663000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>722000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>690000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>684000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>711000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>710000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>683000</v>
-      </c>
-      <c r="W83" s="3">
-        <v>671000</v>
       </c>
       <c r="X83" s="3">
         <v>671000</v>
       </c>
       <c r="Y83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>814000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>799000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>677000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>723000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>820000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>711000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>650000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>643000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>750000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>716000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>676000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>692000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>720000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>665000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>707000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8600,8 +8801,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8716,8 +8920,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8832,8 +9039,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8948,8 +9158,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9064,124 +9277,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4972000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5408000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4985000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3705000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4825000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4302000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5754000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4088000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5100000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4904000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5341000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3863000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3574000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4070000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3713000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3246000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5121000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4643000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4121000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4087000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5424000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4739000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4806000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4064000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4364000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4169000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4151000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9222,124 +9441,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1167000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-996000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-859000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-925000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-993000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-783000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-797000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-817000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-925000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-734000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-730000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-708000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-890000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-692000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-747000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-626000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-714000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-656000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-567000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-850000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-658000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-731000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-605000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-814000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9454,8 +9677,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9570,124 +9796,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1228000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1535000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1063000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-726000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-921000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-518000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-762000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-798000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-490000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-832000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-682000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-960000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-791000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-665000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-549000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-829000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-659000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-725000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-650000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5079000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>647000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>573000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>97000</v>
       </c>
       <c r="AH94" s="3">
         <v>97000</v>
       </c>
       <c r="AI94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>100000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9728,8 +9960,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9766,86 +9999,89 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3">
         <v>566000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AI96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9960,8 +10196,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10076,8 +10315,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10192,352 +10434,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4088000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2239000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3616000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4215000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5571000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-634000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5945000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E101" s="3">
         <v>116000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-83000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-119000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>107000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-156000</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>53000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-235000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-185000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-56000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>53000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-235000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-185000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-56000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-129000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-127000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>36000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-81000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>115000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>31000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>40000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-170000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>56000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>7000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>18000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>82000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>47000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>82000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>159000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>128000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-345000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1614000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>440000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1114000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1927000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2676000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2654000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1488000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>650000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>742000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>144000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-504000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1174000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>82000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>281000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>788000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>9114000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5065000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1501000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>354000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>PG</t>
   </si>
@@ -656,503 +656,515 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="41" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21235000</v>
+      </c>
+      <c r="E8" s="3">
         <v>22208000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22386000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20889000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19776000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21882000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21737000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20532000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20195000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21441000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21871000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20553000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20068000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>20773000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>20612000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>19515000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19381000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20953000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>20338000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>18946000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>18109000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>19745000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>19318000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>17698000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>17214000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>18240000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>17798000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>17094000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>16462000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>17438000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>16690000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>16503000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>16281000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>17395000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>16653000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>16079000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>15605000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>16856000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>16518000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10584000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10654000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10787000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10572000</v>
       </c>
-      <c r="G9" s="3">
-        <v>9671000</v>
-      </c>
       <c r="H9" s="3">
+        <v>9694000</v>
+      </c>
+      <c r="I9" s="3">
         <v>10418000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10421000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10100000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9855000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10144000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10501000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10453000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10404000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10897000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10846000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10802000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10326000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10664000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10365000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9791000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>8922000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9253000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>9142000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>8659000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>8518000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8806000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>8653000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>8410000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>8342000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>8776000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8420000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>17634000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8213000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>17270000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>16380000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8115000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>7704000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>8150000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>7973000</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10651000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11554000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11599000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>10317000</v>
       </c>
-      <c r="G10" s="3">
-        <v>10105000</v>
-      </c>
       <c r="H10" s="3">
+        <v>10082000</v>
+      </c>
+      <c r="I10" s="3">
         <v>11464000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11316000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10432000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10340000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11297000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11370000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>10100000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9664000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9876000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9766000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8713000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9055000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10289000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9973000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9155000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>9187000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10492000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10176000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>9039000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8696000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9434000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>9145000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8684000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8120000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8662000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8270000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-1131000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8068000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>125000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>273000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7964000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>7901000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8706000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>8545000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1206,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1205,11 +1218,11 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3">
         <v>2100000</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1217,11 +1230,11 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -1229,11 +1242,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3">
         <v>2000000</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
@@ -1313,8 +1326,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,22 +1448,25 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E14" s="3">
         <v>369000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>215000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>132000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>55000</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1455,23 +1474,23 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>665000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1341000</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>338000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1482,20 +1501,20 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1503,98 +1522,101 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>362000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>222000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>105000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>93000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8985000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>116000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>177000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-218000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>554000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>205000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>154000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>157000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>249000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>157000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>175000</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>785000</v>
+      </c>
+      <c r="E15" s="3">
         <v>802000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>761000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>723000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>690000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>706000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>728000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>761000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>712000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>721000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>702000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>706000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>692000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1670,8 +1692,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,246 +1735,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16341000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16368000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16212000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15636000</v>
       </c>
-      <c r="G17" s="3">
-        <v>15169000</v>
-      </c>
       <c r="H17" s="3">
+        <v>15067000</v>
+      </c>
+      <c r="I17" s="3">
         <v>15987000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15797000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15585000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15735000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15562000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16006000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15731000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15734000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15988000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15673000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15917000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>15357000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15785000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15315000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>15406000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>14324000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>14365000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>14037000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>14221000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>13764000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>13763000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>13509000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>22287000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13235000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>13551000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12782000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>13916000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>12985000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>13476000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>13005000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>13130000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>12245000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>12981000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>12747000</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4894000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5840000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6174000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5253000</v>
       </c>
-      <c r="G18" s="3">
-        <v>4607000</v>
-      </c>
       <c r="H18" s="3">
+        <v>4709000</v>
+      </c>
+      <c r="I18" s="3">
         <v>5895000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5940000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4947000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4460000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5879000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5865000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4822000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4334000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4785000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4939000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3598000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4024000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5168000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5023000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3540000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3785000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5380000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5281000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3477000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3450000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4477000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4289000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-5193000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3227000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3887000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3908000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2587000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3296000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3919000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3648000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2949000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3360000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3875000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>3771000</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1991,603 +2023,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-415000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-55000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-164000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>492000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-214000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-72000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>698000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>299000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-262000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-73000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>127000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-93000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>221000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>181000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>167000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>156000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>177000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>121000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>141000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>198000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-360000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>152000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>141000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>148000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>155000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>162000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>239000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>182000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>167000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>161000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>90000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>358000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>218000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>94000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>72000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-497000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>98000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6094000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6697000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7099000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5484000</v>
       </c>
-      <c r="G21" s="3">
-        <v>5511000</v>
-      </c>
       <c r="H21" s="3">
+        <v>5456000</v>
+      </c>
+      <c r="I21" s="3">
         <v>6673000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5970000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5409000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5434000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6673000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6601000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5401000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5119000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5659000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5783000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4487000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4870000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6029000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5855000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4391000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4666000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5691000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6104000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4432000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4397000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5309000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5174000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-4134000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4120000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4704000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4712000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3311000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4102000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>4953000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4558000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3763000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>4097000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>4085000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>4597000</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E22" s="3">
         <v>220000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>197000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>212000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>217000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>240000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>238000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>220000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>233000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>248000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>225000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>240000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>222000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>171000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>123000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>115000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>109000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>106000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>109000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>117000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>106000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>143000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>136000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>157000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>100000</v>
       </c>
       <c r="AB22" s="3">
         <v>100000</v>
       </c>
       <c r="AC22" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AD22" s="3">
         <v>108000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>111000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>131000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>138000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>129000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>272000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>133000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>244000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>115000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>116000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>96000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>122000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>131000</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4989000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5421000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6034000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4521000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4660000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5846000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5139000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3870000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4593000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4496000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5802000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4233000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4288000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4835000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4997000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3650000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4071000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5239000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5035000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3564000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3877000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4877000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5297000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3461000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3498000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4532000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4343000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5065000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3278000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3916000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3940000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2289000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3253000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4033000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3751000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2927000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>3336000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>3256000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>3738000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1090000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1253000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>895000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>868000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1187000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1152000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>726000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>812000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1003000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1246000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>841000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>864000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>876000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1034000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>592000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>704000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>997000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>909000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>656000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>628000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>990000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>989000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>675000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>541000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>789000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>726000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>172000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>502000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>729000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>499000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>613000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>872000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>881000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>725000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>780000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>695000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>863000</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2705,246 +2753,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3950000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4331000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4781000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3626000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3792000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4659000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3987000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3144000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3781000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3493000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4556000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3392000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3424000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3959000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3963000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3058000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3367000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4242000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4126000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2908000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3249000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3887000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4308000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2786000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2957000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3743000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3617000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5237000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2776000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3216000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3211000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1790000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2640000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3161000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2870000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2202000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2556000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2561000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>2875000</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3860000</v>
+      </c>
+      <c r="E27" s="3">
         <v>4246000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4677000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3539000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3698000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4558000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3887000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3062000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3685000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3398000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4451000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3312000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3328000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3868000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2979000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3287000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4153000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4042000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2832000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3204000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3788000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4211000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2730000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2853000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3528000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3129000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3133000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1724000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2537000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3033000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2791000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2152000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2462000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>2479000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>2769000</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3062,8 +3119,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3139,17 +3199,17 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3157,18 +3217,18 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>100000</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-100000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-600000</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
         <v>0</v>
       </c>
@@ -3176,13 +3236,16 @@
         <v>0</v>
       </c>
       <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3">
         <v>5335000</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-118000</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3300,8 +3363,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3419,246 +3485,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>415000</v>
+      </c>
+      <c r="E32" s="3">
         <v>55000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>164000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-492000</v>
       </c>
-      <c r="G32" s="3">
-        <v>214000</v>
-      </c>
       <c r="H32" s="3">
+        <v>57000</v>
+      </c>
+      <c r="I32" s="3">
         <v>72000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-698000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-299000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>262000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>73000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-127000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>93000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-221000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-181000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-167000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-156000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-177000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-121000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-141000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-198000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>360000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-152000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-141000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-148000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-155000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-162000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-239000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-182000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-167000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-161000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>26000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-90000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-358000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-218000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-94000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-72000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>497000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-98000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3932000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4319000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4750000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3615000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3769000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4630000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3959000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3137000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3754000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3468000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4521000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3384000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3397000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3868000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2979000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3287000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4153000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4042000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2832000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3204000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3788000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4211000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2730000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2853000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3528000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3129000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3133000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1824000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2437000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2433000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2791000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2152000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2462000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>7814000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3776,251 +3851,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3932000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4319000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4750000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3615000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3769000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4630000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3959000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3137000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3754000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3468000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4521000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3384000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3397000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3868000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2979000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3287000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4153000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4042000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2832000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3204000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3788000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4211000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2730000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2853000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3528000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3129000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3133000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1824000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2437000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2433000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2791000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2152000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2462000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>7814000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4062,8 +4146,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4105,127 +4190,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12306000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10825000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11171000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9556000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9116000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10230000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12156000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9482000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6828000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7890000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9733000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8246000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7596000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6854000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6710000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7214000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8526000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11544000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10370000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10288000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10007000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11941000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13392000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16181000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15393000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6279000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>9304000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4239000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2738000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3696000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2545000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2569000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5326000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7432000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>5024000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>5569000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5817000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>6051000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>7456000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4308,281 +4397,290 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>6048000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7085000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8421000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>8708000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>9281000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>10208000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>11326000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>10983000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>9568000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>8510000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>7403000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>6615000</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6322000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6279000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6487000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6185000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6139000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6234000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6314000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6118000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6124000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6334000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6215000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>5471000</v>
       </c>
       <c r="O43" s="3">
         <v>5471000</v>
       </c>
       <c r="P43" s="3">
+        <v>5471000</v>
+      </c>
+      <c r="Q43" s="3">
         <v>5767000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5720000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5143000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5513000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5241000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5662000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4725000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4861000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4819000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5043000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4178000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4640000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>5196000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5143000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4951000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5198000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5055000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5035000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4686000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5149000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5182000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4942000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4594000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>4358000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>4729000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>4713000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7853000</v>
+      </c>
+      <c r="E44" s="3">
         <v>7818000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7848000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7550000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7400000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7020000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7287000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7016000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7078000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7152000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7117000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7073000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7483000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7541000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7590000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6924000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7101000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6673000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6307000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5983000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6002000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>5957000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>5707000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>5498000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5330000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5521000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5465000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5017000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5358000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5281000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5182000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4738000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5207000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5131000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5023000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4624000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4754000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4787000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>4999000</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4592,11 +4690,11 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>1000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -4622,205 +4720,211 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2501000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2372000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2276000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2087000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1997000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2095000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1738000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1938000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1884000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2130000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1777000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1921000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2013000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2218000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1933000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1978000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1876000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2046000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2070000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2143000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2124000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2139000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2446000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2602000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>11388000</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27987000</v>
+      </c>
+      <c r="E46" s="3">
         <v>26588000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>27118000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>25392000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24435000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>25642000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27449000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24709000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22458000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23111000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24940000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22648000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22305000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21866000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22521000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21653000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23416000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>25545000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>24336000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>23091000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>22608000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>24655000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>26026000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>27987000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>27140000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18917000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>21925000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>22473000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>22312000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>24431000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>23346000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>23320000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>27960000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>31214000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>28096000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>26494000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>25885000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>25572000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>35171000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4857,23 +4961,23 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>91000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>60000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>66000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>113000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>126000</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -4887,8 +4991,8 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4938,246 +5042,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24574000</v>
+      </c>
+      <c r="E48" s="3">
         <v>24487000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24119000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24822000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22728000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22074000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22506000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23027000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22027000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22132000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21636000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22690000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21564000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21167000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20593000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21195000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21323000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21357000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21392000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21686000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21103000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>21416000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>20876000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21542000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>21314000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22153000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>21788000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>21271000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>20993000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>20822000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20590000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20600000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20925000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20420000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>20108000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>19893000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>19219000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>18778000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>19310000</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>62890000</v>
+      </c>
+      <c r="E49" s="3">
         <v>63402000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>63461000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>63560000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>62312000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>61731000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>63023000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>62350000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>62760000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>63218000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>63876000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>64442000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>64550000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>63545000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>62226000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>63379000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>64623000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>63853000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>63997000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>64566000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>64270000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>65245000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>64383000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>63693000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>63451000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>63978000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>63607000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>64488000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>72589000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>72879000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>69144000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>69077000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>70304000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>69848000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>69451000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>68886000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>67835000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>67643000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>68887000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5295,8 +5408,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5414,127 +5530,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12927000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12809000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12901000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11457000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13509000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13192000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13504000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12284000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12353000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12248000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12079000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11049000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11341000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11077000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10876000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10868000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10729000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10661000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9944000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9964000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8797000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8796000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8614000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>7478000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6655000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6675000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6738000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>6863000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5779000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5555000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>5360000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5313000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5180000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5162000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5196000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5133000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5152000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5040000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5675000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5652,127 +5774,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128378000</v>
+      </c>
+      <c r="E54" s="3">
         <v>127286000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>127599000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>125231000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122984000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>122639000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>126482000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>122370000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119598000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120709000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>122531000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120829000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>119851000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>117715000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>116282000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>117208000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>120217000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>121416000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>119669000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>119307000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>116778000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>120112000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>119899000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>120700000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>118560000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>111723000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>114058000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>115095000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>121673000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>123687000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>118440000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>118310000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>124369000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>126644000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>122851000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>120406000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>118091000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>117033000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>129043000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5814,8 +5942,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5857,260 +5986,267 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15030000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15173000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15609000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15227000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14512000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14495000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15350000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15364000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13691000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14234000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14435000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14598000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13790000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14153000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14845000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14882000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14175000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14154000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14223000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>13720000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12134000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>12027000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>11935000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>12071000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10464000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>10781000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10951000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>11260000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10207000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10266000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10243000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>10344000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9716000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9740000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9458000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9632000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>8076000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>8300000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>9024000</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13174000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11062000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11631000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10395000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9889000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9424000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10409000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7465000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7729000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10616000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11811000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11082000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>13717000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14300000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11717000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>8645000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9902000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>13331000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11989000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>8889000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>8773000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>8586000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7707000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11183000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>12701000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>9153000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9352000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9697000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8911000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>12113000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10508000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>10423000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>12862000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>15547000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>14026000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>13554000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>13781000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>13007000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>12215000</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4286000</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
@@ -6118,11 +6254,11 @@
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>4183000</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>8</v>
@@ -6130,449 +6266,461 @@
       <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>3917000</v>
       </c>
-      <c r="O59" s="3" t="s">
+      <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10293000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>10056000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9554000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>10324000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>10542000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10377000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>10523000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11109000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11131000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10366000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9722000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9731000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10230000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9950000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9054000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9252000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8868000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8469000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7470000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8133000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7820000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>7240000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7024000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7225000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>7584000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>11162000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38235000</v>
+      </c>
+      <c r="E60" s="3">
         <v>36699000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37995000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36058000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34248000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33797000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36420000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33627000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32340000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35950000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>37158000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35756000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38030000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38746000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36618000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33081000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>34401000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>38027000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>36589000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>33132000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>32016000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31744000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>30008000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32976000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>32896000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>30164000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>30253000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>30011000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>28370000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>31247000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29220000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>28237000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30711000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>33107000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30724000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>30210000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>29082000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>28891000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>32401000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23852000</v>
+      </c>
+      <c r="E61" s="3">
         <v>25577000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>24315000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>26131000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>24252000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>25263000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>25744000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26260000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>24253000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23096000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>24069000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>25418000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>22874000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20582000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>21286000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>22848000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23767000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>22322000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>20558000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>23099000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>21053000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>22514000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>23948000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>23537000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>23310000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>18985000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>20161000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>20395000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>21359000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>21514000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>20779000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>20863000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>22437000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>22186000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>20188000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18038000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>16633000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>16460000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>18910000</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5513000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5719000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5845000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1267000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5458000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5411000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5758000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1872000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6388000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6616000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6477000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2306000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7104000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13662000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>14044000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14425000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>16303000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16174000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>16114000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>16422000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16790000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>17314000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>17367000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>17309000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>16413000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>16666000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>16660000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>17110000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>16392000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>16483000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>15937000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>16327000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>16275000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>16630000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>16524000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>16380000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>17828000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>17938000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>18781000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6690,8 +6838,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6809,8 +6960,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6928,127 +7082,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>73647000</v>
+      </c>
+      <c r="E66" s="3">
         <v>73969000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74048000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72947000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70439000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>71196000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74342000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71812000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>69265000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71881000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>74518000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73764000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74430000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>73260000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>72207000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>70619000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>74739000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>76798000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>73558000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>72929000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70182000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>71931000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>71717000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>74179000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>73020000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66185000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>67480000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>67901000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>66601000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>69697000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>66204000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>66017000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>70054000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>72532000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>68033000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>65222000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>64251000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>63973000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>70781000</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7090,8 +7250,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7209,8 +7370,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7328,127 +7492,133 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E70" s="3">
         <v>767000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>770000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>777000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>781000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>788000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>791000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>798000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>801000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>809000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>812000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>819000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>822000</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>831000</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>834000</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>843000</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>846000</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>856000</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>859000</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>870000</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>873000</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>885000</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="Z70" s="3">
         <v>888000</v>
       </c>
-      <c r="Z70" s="3">
+      <c r="AA70" s="3">
         <v>897000</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>900000</v>
       </c>
-      <c r="AB70" s="3">
+      <c r="AC70" s="3">
         <v>911000</v>
       </c>
-      <c r="AC70" s="3">
+      <c r="AD70" s="3">
         <v>915000</v>
       </c>
-      <c r="AD70" s="3">
+      <c r="AE70" s="3">
         <v>928000</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>933000</v>
       </c>
-      <c r="AF70" s="3">
+      <c r="AG70" s="3">
         <v>946000</v>
       </c>
-      <c r="AG70" s="3">
+      <c r="AH70" s="3">
         <v>951000</v>
       </c>
-      <c r="AH70" s="3">
+      <c r="AI70" s="3">
         <v>967000</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>972000</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>986000</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>991000</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>1006000</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>1010000</v>
       </c>
-      <c r="AN70" s="3">
+      <c r="AO70" s="3">
         <v>1024000</v>
       </c>
-      <c r="AO70" s="3">
+      <c r="AP70" s="3">
         <v>1029000</v>
       </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7566,127 +7736,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>135424000</v>
+      </c>
+      <c r="E72" s="3">
         <v>133981000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>132212000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>129973000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>128919000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>127544000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>125361000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>123811000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>123132000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>121617000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>120443000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>118170000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>117082000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>115858000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>114163000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>112429000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>111645000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>110393000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>108361000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>106374000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>105674000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>104361000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>102539000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>100239000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>99474000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>98414000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>96625000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>94918000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>102103000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>101170000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>99831000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>98641000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>98623000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>97881000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>97197000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>96124000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>95736000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>94945000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>88855000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7804,8 +7980,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7923,8 +8102,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8042,127 +8224,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>53746000</v>
+      </c>
+      <c r="E76" s="3">
         <v>52274000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>52500000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51235000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51491000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>50380000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>51049000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>49488000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>49257000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47725000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>46880000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>45958000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44318000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>43624000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43241000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45746000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44632000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>43762000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45252000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>45508000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>45723000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>47296000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>47294000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>45624000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>44640000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>44627000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>45663000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>46266000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>54139000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>53044000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>51285000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>51326000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>53343000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>53126000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>53827000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>54178000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>52830000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>52036000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>57233000</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8280,251 +8468,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3932000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4319000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4750000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3615000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3769000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4630000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3959000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3137000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3754000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3468000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4521000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3384000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3397000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3863000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3868000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2979000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3287000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4153000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4042000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2832000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3204000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3788000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4211000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2730000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2853000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3653000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3528000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5309000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2681000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3129000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3133000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1824000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2437000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2433000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2791000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2152000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2462000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>7814000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>2651000</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8566,127 +8763,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>612000</v>
+      </c>
+      <c r="E83" s="3">
         <v>626000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>645000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>678000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>628000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>637000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>615000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>620000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>610000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>574000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>583000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>640000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>611000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>653000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>663000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>722000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>690000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>684000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>711000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>710000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>683000</v>
-      </c>
-      <c r="X83" s="3">
-        <v>671000</v>
       </c>
       <c r="Y83" s="3">
         <v>671000</v>
       </c>
       <c r="Z83" s="3">
+        <v>671000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>814000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>799000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>677000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>723000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>820000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>711000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>650000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>643000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>750000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>716000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>676000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>692000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>720000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>665000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>707000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8804,8 +9005,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8923,8 +9127,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9042,8 +9249,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9161,8 +9371,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9280,127 +9493,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4045000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4972000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5408000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4985000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3705000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4825000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4302000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5754000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4088000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5100000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4904000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5341000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3863000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3574000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4070000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3713000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3246000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5121000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4643000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4121000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4087000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5424000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4739000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4806000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4064000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4364000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4169000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4151000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3517000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4007000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3567000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4199000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3353000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3684000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3631000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3688000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3040000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3000000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3025000</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9442,127 +9661,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1019000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1167000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-996000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-859000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-925000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-993000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-783000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-797000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-817000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-925000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-734000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-730000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-708000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-890000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-692000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-747000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-626000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1091000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-714000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-656000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-567000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-850000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-658000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-731000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-605000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1079000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-814000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-752000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-701000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-907000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-910000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-768000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1132000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-801000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-745000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-684000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9680,8 +9903,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9799,127 +10025,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-665000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1228000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1535000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1063000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-726000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-921000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1108000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-518000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-762000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1002000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1222000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-798000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1380000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-490000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-832000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-682000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1776000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-960000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1006000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-791000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-665000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-549000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-829000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-659000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-725000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-650000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5079000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>647000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>573000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3845000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-865000</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>97000</v>
       </c>
       <c r="AI94" s="3">
         <v>97000</v>
       </c>
       <c r="AJ94" s="3">
+        <v>97000</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-1171000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2534000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1866000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1802000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>100000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2121000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9961,8 +10193,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,86 +10235,89 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>566000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2184000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2171000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2112000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-2197000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-2143000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1959000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1964000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-2028000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-2035000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1859000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1867000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1937000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1858000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1850000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1861000</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-1813000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-1813000</v>
       </c>
       <c r="AK96" s="3">
+        <v>-1813000</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-1823000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1826000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1773000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-1851000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10199,8 +10435,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10318,8 +10557,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10437,361 +10679,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1827000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4088000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2239000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3616000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4215000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5571000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-634000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2499000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4269000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6049000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2038000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3893000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1753000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2993000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3507000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4158000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4432000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2858000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3428000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3085000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5275000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6441000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6730000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3399000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5945000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6795000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4118000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5066000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1032000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2656000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6861000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5638000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-152000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1724000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2229000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4232000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-507000</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>122000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-260000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>116000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-83000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-119000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>107000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-156000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>53000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-235000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-185000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-56000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>53000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-235000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-185000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-56000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-129000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-127000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>36000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-81000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>115000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>31000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>40000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-170000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>56000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>7000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-43000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-70000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-192000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>82000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>47000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>82000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>159000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>128000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-273000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-43000</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-345000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1614000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>440000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1114000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1927000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2676000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2654000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1062000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1844000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1488000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>650000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>742000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>144000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-504000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1312000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3018000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1174000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>82000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>281000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1934000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1451000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2789000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>788000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9114000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3025000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>5065000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1501000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-958000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1151000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-24000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2757000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>2408000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-545000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-234000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1405000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>354000</v>
       </c>
     </row>
